--- a/meal glucose bread and bread + inhibitor.xlsx
+++ b/meal glucose bread and bread + inhibitor.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{3E4A4EC0-DEEF-4FC1-907E-2B747F6C8CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9017196C-154B-4142-BE8F-C7590734856E}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{3E4A4EC0-DEEF-4FC1-907E-2B747F6C8CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55C5D246-7270-4621-9D7E-F7DA655E5ED9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -995,7 +995,7 @@
       <c r="B5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="7">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AD8" s="10"/>
       <c r="AE8" s="11"/>
@@ -1123,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="7">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AD10" s="10"/>
       <c r="AE10" s="11"/>

--- a/meal glucose bread and bread + inhibitor.xlsx
+++ b/meal glucose bread and bread + inhibitor.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{3E4A4EC0-DEEF-4FC1-907E-2B747F6C8CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9017196C-154B-4142-BE8F-C7590734856E}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{3E4A4EC0-DEEF-4FC1-907E-2B747F6C8CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9E8B7AD-8984-4CB2-BF0F-FE80460E91EB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1166,7 +1166,7 @@
         <v>27</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>2</v>

--- a/meal glucose bread and bread + inhibitor.xlsx
+++ b/meal glucose bread and bread + inhibitor.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{3E4A4EC0-DEEF-4FC1-907E-2B747F6C8CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9017196C-154B-4142-BE8F-C7590734856E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{05CE18E0-1986-4BEA-BEEE-EF7DB2C88548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -995,7 +995,7 @@
       <c r="B5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="7">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AD8" s="10"/>
       <c r="AE8" s="11"/>
@@ -1123,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="7">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AD10" s="10"/>
       <c r="AE10" s="11"/>
@@ -1749,10 +1749,10 @@
         <v>0.5</v>
       </c>
       <c r="S20" s="17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" s="17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="U20" s="19">
         <v>0.5</v>
@@ -2243,13 +2243,13 @@
         <v>100</v>
       </c>
       <c r="R25" s="17">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S25" s="17">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T25" s="17">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="U25" s="19">
         <v>50</v>
@@ -2740,13 +2740,13 @@
         <v>100</v>
       </c>
       <c r="R30" s="17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S30" s="17">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T30" s="17">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="U30" s="19">
         <v>10</v>

--- a/meal glucose bread and bread + inhibitor.xlsx
+++ b/meal glucose bread and bread + inhibitor.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{05CE18E0-1986-4BEA-BEEE-EF7DB2C88548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="14_{069F9307-C162-4C9A-BE96-B7D55D7C49CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67A44B3B-F1F5-4847-878F-7873F10F784E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <definedName name="_1_water" localSheetId="12">'resistant starch'!$B$1</definedName>
     <definedName name="_1_water" localSheetId="11">'slow starch'!$B$1</definedName>
     <definedName name="_1_water">sucrose!$B$1</definedName>
-    <definedName name="milk_choc">meal!$G$16</definedName>
+    <definedName name="milk_choc">meal!$G$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="119">
   <si>
     <t>Inlezen maaltijden</t>
   </si>
@@ -400,6 +400,9 @@
   <si>
     <t>I_nc     non competitive alpha amylase inhibitor</t>
   </si>
+  <si>
+    <t>citric acid</t>
+  </si>
 </sst>
 </file>
 
@@ -546,7 +549,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -569,6 +572,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -908,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI87"/>
+  <dimension ref="A1:AJ89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="7"/>
@@ -925,12 +929,12 @@
     <col min="19" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>76</v>
       </c>
@@ -941,7 +945,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>30</v>
       </c>
@@ -984,11 +988,12 @@
       <c r="AD4" s="8"/>
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
-      <c r="AG4" s="8"/>
+      <c r="AG4" s="1"/>
       <c r="AH4" s="8"/>
       <c r="AI4" s="8"/>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ4" s="8"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
@@ -1015,7 +1020,7 @@
       <c r="Y5" s="8"/>
       <c r="AA5" s="8"/>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>0</v>
       </c>
@@ -1042,7 +1047,7 @@
       <c r="Y6" s="8"/>
       <c r="AA6" s="8"/>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>1</v>
       </c>
@@ -1069,9 +1074,9 @@
       <c r="Y7" s="8"/>
       <c r="AA7" s="8"/>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="B8" s="9">
         <v>1</v>
@@ -1089,9 +1094,9 @@
       <c r="AE8" s="11"/>
       <c r="AF8" s="11"/>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="B9" s="9">
         <v>15</v>
@@ -1109,9 +1114,9 @@
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="B10" s="9">
         <v>1</v>
@@ -1129,9 +1134,9 @@
       <c r="AE10" s="11"/>
       <c r="AF10" s="11"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
-        <v>1001</v>
+        <v>601</v>
       </c>
       <c r="B11" s="9">
         <v>15</v>
@@ -1158,9 +1163,9 @@
       <c r="AE11" s="11"/>
       <c r="AF11" s="11"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
-        <v>1002</v>
+        <v>602</v>
       </c>
       <c r="B12" s="9">
         <v>27</v>
@@ -1187,2017 +1192,2094 @@
       <c r="AE12" s="11"/>
       <c r="AF12" s="11"/>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>900</v>
+      </c>
+      <c r="B13" s="9">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>250</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" s="20">
+        <v>50</v>
+      </c>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="AA13"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="11"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
         <v>9999</v>
       </c>
-      <c r="B13" s="8"/>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:35" s="8" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="1:36" s="8" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D16" s="12">
         <v>1</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E16" s="12">
         <v>2</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F16" s="12">
         <v>3</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G16" s="12">
         <v>4</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H16" s="12">
         <v>5</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I16" s="12">
         <v>6</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J16" s="12">
         <v>7</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K16" s="12">
         <v>8</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L16" s="12">
         <v>9</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M16" s="12">
         <v>10</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N16" s="12">
         <v>11</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O16" s="12">
         <v>12</v>
       </c>
-      <c r="P15" s="12">
+      <c r="P16" s="12">
         <v>13</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="Q16" s="12">
         <v>14</v>
       </c>
-      <c r="R15" s="12">
+      <c r="R16" s="12">
         <v>15</v>
       </c>
-      <c r="S15" s="12">
+      <c r="S16" s="12">
         <v>16</v>
       </c>
-      <c r="T15" s="12">
+      <c r="T16" s="12">
         <v>17</v>
       </c>
-      <c r="U15" s="12">
+      <c r="U16" s="12">
         <v>18</v>
       </c>
-      <c r="V15" s="12">
+      <c r="V16" s="12">
         <v>19</v>
       </c>
-      <c r="W15" s="12">
+      <c r="W16" s="12">
         <v>20</v>
       </c>
-      <c r="X15" s="12">
+      <c r="X16" s="12">
         <v>21</v>
       </c>
-      <c r="Y15" s="12">
+      <c r="Y16" s="12">
         <v>22</v>
       </c>
-      <c r="Z15" s="12">
+      <c r="Z16" s="12">
         <v>23</v>
       </c>
-      <c r="AA15" s="12">
+      <c r="AA16" s="12">
         <v>24</v>
       </c>
-      <c r="AB15" s="12">
+      <c r="AB16" s="12">
         <v>25</v>
       </c>
-      <c r="AC15" s="2">
+      <c r="AC16" s="2">
         <v>26</v>
       </c>
-      <c r="AD15" s="1">
+      <c r="AD16" s="1">
         <v>27</v>
       </c>
-      <c r="AE15" s="1">
+      <c r="AE16" s="1">
         <v>28</v>
       </c>
-      <c r="AF15" s="1">
+      <c r="AF16" s="1">
         <v>29</v>
       </c>
-      <c r="AG15" s="8">
+      <c r="AG16" s="1">
+        <v>30</v>
+      </c>
+      <c r="AH16" s="8">
         <v>9999</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="11" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F17" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H17" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I17" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J17" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K17" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="8" t="s">
+      <c r="M17" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="N17" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="O17" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="P16" s="8" t="s">
+      <c r="P17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="Q17" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="R16" s="16" t="s">
+      <c r="R17" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="S16" s="17" t="s">
+      <c r="S17" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="T16" s="17" t="s">
+      <c r="T17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="U16" s="18" t="s">
+      <c r="U17" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="V16" s="18" t="s">
+      <c r="V17" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="W16" s="18" t="s">
+      <c r="W17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="X16" t="s">
+      <c r="X17" t="s">
         <v>8</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="Y17" t="s">
         <v>8</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="Z17" t="s">
         <v>8</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AA17" t="s">
         <v>8</v>
       </c>
-      <c r="AB16" s="1" t="s">
+      <c r="AB17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AC16" s="1" t="s">
+      <c r="AC17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AD16" s="1" t="s">
+      <c r="AD17" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AE16" s="1" t="s">
+      <c r="AE17" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="AF16" s="1" t="s">
+      <c r="AF17" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="AG17" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D18" s="7">
         <f>water!D4</f>
         <v>7</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E18" s="7">
         <f>glucose!D4</f>
         <v>7</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F18" s="7">
         <f>sucrose!D4</f>
         <v>7</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G18" s="7">
         <f>'milk choc'!D4</f>
         <v>7</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H18" s="13">
         <f>'milk chocolate arabinose'!D4</f>
         <v>7</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I18" s="7">
         <f>'gastic milk choc'!D4</f>
         <v>7</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J18" s="7">
         <f>'gastic milk choc arab'!D4</f>
         <v>7</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K18" s="7">
         <f>emulsie!D4</f>
         <v>7</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L18" s="7">
         <f>arabinose!D4</f>
         <v>7</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M18" s="7">
         <v>7</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N18" s="7">
         <v>7</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O18" s="7">
         <v>7</v>
       </c>
-      <c r="P17">
+      <c r="P18">
         <v>7</v>
       </c>
-      <c r="Q17">
+      <c r="Q18">
         <v>7</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R18" s="16">
         <v>7</v>
       </c>
-      <c r="S17" s="16">
+      <c r="S18" s="16">
         <v>7</v>
       </c>
-      <c r="T17" s="16">
+      <c r="T18" s="16">
         <v>7</v>
       </c>
-      <c r="U17" s="18">
+      <c r="U18" s="18">
         <v>7</v>
       </c>
-      <c r="V17" s="18">
+      <c r="V18" s="18">
         <v>7</v>
       </c>
-      <c r="W17" s="18">
+      <c r="W18" s="18">
         <v>7</v>
       </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="8">
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="8">
         <v>7</v>
       </c>
-      <c r="AC17" s="1">
+      <c r="AC18" s="1">
         <v>7</v>
       </c>
-      <c r="AD17" s="1">
+      <c r="AD18" s="1">
         <v>7</v>
       </c>
-      <c r="AE17" s="1">
+      <c r="AE18" s="1">
         <v>7</v>
       </c>
-      <c r="AF17" s="1">
+      <c r="AF18" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="AG18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D19" s="7">
         <f>water!D5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E19" s="7">
         <v>1</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F19" s="7">
         <v>1</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G19" s="7">
         <f>'milk choc'!D5</f>
         <v>1</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H19" s="13">
         <f>'milk chocolate arabinose'!D5</f>
         <v>1</v>
       </c>
-      <c r="I18" s="7">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0</v>
-      </c>
-      <c r="K18" s="7">
+      <c r="I19" s="7">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7">
         <f>emulsie!D5</f>
         <v>0</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L19" s="7">
         <f>arabinose!D5</f>
         <v>1</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M19" s="7">
         <v>2</v>
       </c>
-      <c r="N18" s="7">
+      <c r="N19" s="7">
         <v>1</v>
       </c>
-      <c r="O18" s="7">
+      <c r="O19" s="7">
         <v>1</v>
       </c>
-      <c r="P18">
+      <c r="P19">
         <v>1</v>
       </c>
-      <c r="Q18">
+      <c r="Q19">
         <v>1</v>
       </c>
-      <c r="R18" s="16">
+      <c r="R19" s="16">
         <v>20</v>
       </c>
-      <c r="S18" s="16">
+      <c r="S19" s="16">
         <v>5</v>
       </c>
-      <c r="T18" s="16">
+      <c r="T19" s="16">
         <v>1</v>
       </c>
-      <c r="U18" s="18">
+      <c r="U19" s="18">
         <v>20</v>
       </c>
-      <c r="V18" s="18">
+      <c r="V19" s="18">
         <v>5</v>
       </c>
-      <c r="W18" s="18">
+      <c r="W19" s="18">
         <v>1</v>
       </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="8">
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="8">
         <v>1</v>
       </c>
-      <c r="AC18" s="1">
+      <c r="AC19" s="1">
         <v>1</v>
       </c>
-      <c r="AD18" s="1">
+      <c r="AD19" s="1">
         <v>1</v>
       </c>
-      <c r="AE18" s="1">
+      <c r="AE19" s="1">
         <v>1</v>
       </c>
-      <c r="AF18" s="1">
+      <c r="AF19" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="AG19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D20" s="7">
         <f>water!D6</f>
         <v>1</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E20" s="7">
         <f>glucose!D6</f>
         <v>1</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F20" s="7">
         <f>sucrose!D6</f>
         <v>1</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G20" s="7">
         <f>'milk choc'!D6</f>
         <v>1</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H20" s="13">
         <f>'milk chocolate arabinose'!D6</f>
         <v>1</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I20" s="7">
         <v>1000</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J20" s="7">
         <v>1000</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K20" s="7">
         <f>emulsie!D6</f>
         <v>1</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L20" s="7">
         <f>arabinose!D6</f>
         <v>1</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M20" s="7">
         <v>1000</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N20" s="7">
         <v>1</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O20" s="7">
         <v>1</v>
       </c>
-      <c r="P19">
+      <c r="P20">
         <v>10000</v>
       </c>
-      <c r="Q19">
+      <c r="Q20">
         <v>10000</v>
       </c>
-      <c r="R19" s="16">
+      <c r="R20" s="16">
         <v>1000</v>
       </c>
-      <c r="S19" s="16">
+      <c r="S20" s="16">
         <v>10</v>
       </c>
-      <c r="T19" s="16">
+      <c r="T20" s="16">
         <v>10</v>
       </c>
-      <c r="U19" s="18">
+      <c r="U20" s="18">
         <v>1000</v>
       </c>
-      <c r="V19" s="18">
+      <c r="V20" s="18">
         <v>10</v>
       </c>
-      <c r="W19" s="18">
+      <c r="W20" s="18">
         <v>10</v>
       </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="8">
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="8">
         <v>1</v>
       </c>
-      <c r="AC19" s="1">
+      <c r="AC20" s="1">
         <v>1</v>
       </c>
-      <c r="AD19" s="1">
+      <c r="AD20" s="1">
         <v>1</v>
       </c>
-      <c r="AE19" s="1">
+      <c r="AE20" s="1">
         <v>1</v>
       </c>
-      <c r="AF19" s="1">
+      <c r="AF20" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="AG20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>0.1</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E21" s="1">
         <v>0.1</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F21" s="1">
         <v>0.1</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G21" s="1">
         <v>1</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H21" s="15">
         <v>1</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I21" s="1">
         <v>5</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J21" s="1">
         <v>5</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K21" s="1">
         <f>emulsie!D7</f>
         <v>1</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L21" s="1">
         <v>0.1</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M21" s="1">
         <v>10</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N21" s="1">
         <v>50</v>
       </c>
-      <c r="O20" s="1">
+      <c r="O21" s="1">
         <v>1</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P21" s="1">
         <v>10</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q21" s="1">
         <v>20</v>
       </c>
-      <c r="R20" s="17">
+      <c r="R21" s="17">
         <v>0.5</v>
       </c>
-      <c r="S20" s="17">
+      <c r="S21" s="17">
         <v>10</v>
       </c>
-      <c r="T20" s="17">
+      <c r="T21" s="17">
         <v>10</v>
       </c>
-      <c r="U20" s="19">
+      <c r="U21" s="19">
         <v>0.5</v>
       </c>
-      <c r="V20" s="19">
+      <c r="V21" s="19">
         <v>50</v>
       </c>
-      <c r="W20" s="19">
+      <c r="W21" s="19">
         <v>50</v>
       </c>
-      <c r="X20" s="1">
+      <c r="X21" s="1">
         <v>0.1</v>
       </c>
-      <c r="Y20" s="1">
+      <c r="Y21" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z20" s="1">
+      <c r="Z21" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA20" s="1">
+      <c r="AA21" s="1">
         <v>0.1</v>
       </c>
-      <c r="AB20" s="1">
+      <c r="AB21" s="1">
         <v>1</v>
       </c>
-      <c r="AC20" s="1">
+      <c r="AC21" s="1">
         <v>1</v>
       </c>
-      <c r="AD20" s="1">
+      <c r="AD21" s="1">
         <v>1</v>
       </c>
-      <c r="AE20" s="1">
+      <c r="AE21" s="1">
         <v>1</v>
       </c>
-      <c r="AF20" s="1">
+      <c r="AF21" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C21" s="7" t="s">
+      <c r="AG21" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C22" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D22" s="7">
         <f>water!D8</f>
         <v>0</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E22" s="7">
         <f>glucose!D8</f>
         <v>0</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F22" s="7">
         <f>sucrose!D8</f>
         <v>0</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G22" s="7">
         <f>'milk choc'!D8</f>
         <v>6</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H22" s="13">
         <v>7</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I22" s="7">
         <f>'gastic milk choc'!D8</f>
         <v>0</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J22" s="7">
         <f>'gastic milk choc arab'!D8</f>
         <v>0</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K22" s="7">
         <f>emulsie!D8</f>
         <v>0</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L22" s="7">
         <f>arabinose!D8</f>
         <v>0</v>
       </c>
-      <c r="M21" s="7">
-        <v>0</v>
-      </c>
-      <c r="N21" s="7">
-        <v>0</v>
-      </c>
-      <c r="O21" s="7">
-        <v>0</v>
-      </c>
-      <c r="P21">
+      <c r="M22" s="7">
+        <v>0</v>
+      </c>
+      <c r="N22" s="7">
+        <v>0</v>
+      </c>
+      <c r="O22" s="7">
+        <v>0</v>
+      </c>
+      <c r="P22">
         <v>10</v>
       </c>
-      <c r="Q21">
+      <c r="Q22">
         <v>11</v>
       </c>
-      <c r="R21" s="16">
+      <c r="R22" s="16">
         <v>16</v>
       </c>
-      <c r="S21" s="16">
+      <c r="S22" s="16">
         <v>17</v>
       </c>
-      <c r="T21" s="16">
-        <v>0</v>
-      </c>
-      <c r="U21" s="18">
+      <c r="T22" s="16">
+        <v>0</v>
+      </c>
+      <c r="U22" s="18">
         <v>19</v>
       </c>
-      <c r="V21" s="18">
+      <c r="V22" s="18">
         <v>20</v>
       </c>
-      <c r="W21" s="18">
-        <v>0</v>
-      </c>
-      <c r="X21" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C22" s="7" t="s">
+      <c r="W22" s="18">
+        <v>0</v>
+      </c>
+      <c r="X22" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C23" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D23" s="7">
         <f>water!D9</f>
         <v>0</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E23" s="7">
         <f>glucose!D9</f>
         <v>0</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F23" s="7">
         <f>sucrose!D9</f>
         <v>0</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G23" s="7">
         <v>95</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H23" s="13">
         <v>95</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I23" s="7">
         <f>'gastic milk choc'!D9</f>
         <v>0</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J23" s="7">
         <f>'gastic milk choc arab'!D9</f>
         <v>0</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K23" s="7">
         <f>emulsie!D9</f>
         <v>0</v>
       </c>
-      <c r="L22" s="7">
+      <c r="L23" s="7">
         <f>arabinose!D9</f>
         <v>0</v>
       </c>
-      <c r="M22" s="7">
-        <v>0</v>
-      </c>
-      <c r="N22" s="7">
-        <v>0</v>
-      </c>
-      <c r="O22" s="7">
-        <v>0</v>
-      </c>
-      <c r="P22">
+      <c r="M23" s="7">
+        <v>0</v>
+      </c>
+      <c r="N23" s="7">
+        <v>0</v>
+      </c>
+      <c r="O23" s="7">
+        <v>0</v>
+      </c>
+      <c r="P23">
         <v>50</v>
       </c>
-      <c r="Q22">
+      <c r="Q23">
         <v>100</v>
       </c>
-      <c r="R22" s="16">
+      <c r="R23" s="16">
         <v>60</v>
       </c>
-      <c r="S22" s="16">
+      <c r="S23" s="16">
         <v>100</v>
       </c>
-      <c r="T22" s="16">
-        <v>0</v>
-      </c>
-      <c r="U22" s="18">
+      <c r="T23" s="16">
+        <v>0</v>
+      </c>
+      <c r="U23" s="18">
         <v>70</v>
       </c>
-      <c r="V22" s="18">
+      <c r="V23" s="18">
         <v>100</v>
       </c>
-      <c r="W22" s="18">
-        <v>0</v>
-      </c>
-      <c r="X22" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C23" s="7" t="s">
+      <c r="W23" s="18">
+        <v>0</v>
+      </c>
+      <c r="X23" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C24" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D24" s="7">
         <f>water!D10</f>
         <v>0</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E24" s="7">
         <f>glucose!D10</f>
         <v>0</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F24" s="7">
         <f>sucrose!D10</f>
         <v>0</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G24" s="7">
         <f>'milk choc'!D10</f>
         <v>0</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H24" s="13">
         <f>'milk chocolate arabinose'!D10</f>
         <v>0</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I24" s="7">
         <f>'gastic milk choc'!D10</f>
         <v>0</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J24" s="7">
         <f>'gastic milk choc arab'!D10</f>
         <v>0</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K24" s="7">
         <f>emulsie!D10</f>
         <v>0</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L24" s="7">
         <f>arabinose!D10</f>
         <v>0</v>
       </c>
-      <c r="M23" s="7">
-        <v>0</v>
-      </c>
-      <c r="N23" s="7">
-        <v>0</v>
-      </c>
-      <c r="O23" s="7">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23" s="16">
-        <v>0</v>
-      </c>
-      <c r="S23" s="16">
-        <v>0</v>
-      </c>
-      <c r="T23" s="16">
-        <v>0</v>
-      </c>
-      <c r="U23" s="18">
-        <v>0</v>
-      </c>
-      <c r="V23" s="18">
-        <v>0</v>
-      </c>
-      <c r="W23" s="18">
-        <v>0</v>
-      </c>
-      <c r="X23" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C24" s="7" t="s">
+      <c r="M24" s="7">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7">
+        <v>0</v>
+      </c>
+      <c r="O24" s="7">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" s="16">
+        <v>0</v>
+      </c>
+      <c r="S24" s="16">
+        <v>0</v>
+      </c>
+      <c r="T24" s="16">
+        <v>0</v>
+      </c>
+      <c r="U24" s="18">
+        <v>0</v>
+      </c>
+      <c r="V24" s="18">
+        <v>0</v>
+      </c>
+      <c r="W24" s="18">
+        <v>0</v>
+      </c>
+      <c r="X24" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C25" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D25" s="7">
         <f>water!D11</f>
         <v>0</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E25" s="7">
         <f>glucose!D11</f>
         <v>0</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F25" s="7">
         <f>sucrose!D11</f>
         <v>0</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G25" s="7">
         <f>'milk choc'!D11</f>
         <v>0</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H25" s="13">
         <f>'milk chocolate arabinose'!D11</f>
         <v>0</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I25" s="7">
         <f>'gastic milk choc'!D11</f>
         <v>0</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J25" s="7">
         <f>'gastic milk choc arab'!D11</f>
         <v>0</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K25" s="7">
         <f>emulsie!D11</f>
         <v>0</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L25" s="7">
         <f>arabinose!D11</f>
         <v>0</v>
       </c>
-      <c r="M24" s="7">
-        <v>0</v>
-      </c>
-      <c r="N24" s="7">
-        <v>0</v>
-      </c>
-      <c r="O24" s="7">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24" s="16">
-        <v>0</v>
-      </c>
-      <c r="S24" s="16">
-        <v>0</v>
-      </c>
-      <c r="T24" s="16">
-        <v>0</v>
-      </c>
-      <c r="U24" s="18">
-        <v>0</v>
-      </c>
-      <c r="V24" s="18">
-        <v>0</v>
-      </c>
-      <c r="W24" s="18">
-        <v>0</v>
-      </c>
-      <c r="X24" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="M25" s="7">
+        <v>0</v>
+      </c>
+      <c r="N25" s="7">
+        <v>0</v>
+      </c>
+      <c r="O25" s="7">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" s="16">
+        <v>0</v>
+      </c>
+      <c r="S25" s="16">
+        <v>0</v>
+      </c>
+      <c r="T25" s="16">
+        <v>0</v>
+      </c>
+      <c r="U25" s="18">
+        <v>0</v>
+      </c>
+      <c r="V25" s="18">
+        <v>0</v>
+      </c>
+      <c r="W25" s="18">
+        <v>0</v>
+      </c>
+      <c r="X25" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D26" s="1">
         <v>0.1</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E26" s="1">
         <v>0.1</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F26" s="1">
         <v>0.1</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G26" s="1">
         <v>5</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H26" s="15">
         <v>5</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I26" s="1">
         <v>50</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J26" s="1">
         <v>50</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K26" s="1">
         <f>emulsie!D12</f>
         <v>1</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L26" s="1">
         <v>0.1</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M26" s="1">
         <v>10</v>
       </c>
-      <c r="N25" s="1">
+      <c r="N26" s="1">
         <v>50</v>
       </c>
-      <c r="O25" s="1">
+      <c r="O26" s="1">
         <v>1</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P26" s="1">
         <v>10</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q26" s="1">
         <v>100</v>
       </c>
-      <c r="R25" s="17">
+      <c r="R26" s="17">
         <v>5</v>
       </c>
-      <c r="S25" s="17">
+      <c r="S26" s="17">
         <v>5</v>
       </c>
-      <c r="T25" s="17">
+      <c r="T26" s="17">
         <v>5</v>
       </c>
-      <c r="U25" s="19">
+      <c r="U26" s="19">
         <v>50</v>
       </c>
-      <c r="V25" s="19">
+      <c r="V26" s="19">
         <v>50</v>
       </c>
-      <c r="W25" s="19">
+      <c r="W26" s="19">
         <v>50</v>
       </c>
-      <c r="X25" s="1">
+      <c r="X26" s="1">
         <v>0.1</v>
       </c>
-      <c r="Y25" s="1">
+      <c r="Y26" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z25" s="1">
+      <c r="Z26" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA25" s="1">
+      <c r="AA26" s="1">
         <v>0.1</v>
       </c>
-      <c r="AB25" s="1">
+      <c r="AB26" s="1">
         <v>1</v>
       </c>
-      <c r="AC25" s="1">
+      <c r="AC26" s="1">
         <v>1</v>
       </c>
-      <c r="AD25" s="1">
+      <c r="AD26" s="1">
         <v>1</v>
       </c>
-      <c r="AE25" s="1">
+      <c r="AE26" s="1">
         <v>1</v>
       </c>
-      <c r="AF25" s="1">
+      <c r="AF26" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C26" s="7" t="s">
+      <c r="AG26" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C27" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D27" s="7">
         <f>water!D13</f>
         <v>0</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E27" s="7">
         <f>glucose!D13</f>
         <v>0</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F27" s="7">
         <f>sucrose!D13</f>
         <v>0</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G27" s="7">
         <f>'milk choc'!D13</f>
         <v>6</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H27" s="13">
         <v>7</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I27" s="7">
         <f>'gastic milk choc'!D13</f>
         <v>0</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J27" s="7">
         <f>'gastic milk choc arab'!D13</f>
         <v>0</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K27" s="7">
         <f>emulsie!D13</f>
         <v>0</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L27" s="7">
         <f>arabinose!D13</f>
         <v>0</v>
       </c>
-      <c r="M26" s="7">
-        <v>0</v>
-      </c>
-      <c r="N26" s="7">
-        <v>0</v>
-      </c>
-      <c r="O26" s="7">
-        <v>0</v>
-      </c>
-      <c r="P26">
+      <c r="M27" s="7">
+        <v>0</v>
+      </c>
+      <c r="N27" s="7">
+        <v>0</v>
+      </c>
+      <c r="O27" s="7">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>10</v>
       </c>
-      <c r="Q26">
+      <c r="Q27">
         <v>11</v>
       </c>
-      <c r="R26" s="16">
+      <c r="R27" s="16">
         <v>16</v>
       </c>
-      <c r="S26" s="16">
+      <c r="S27" s="16">
         <v>17</v>
       </c>
-      <c r="T26" s="16">
-        <v>0</v>
-      </c>
-      <c r="U26" s="18">
+      <c r="T27" s="16">
+        <v>0</v>
+      </c>
+      <c r="U27" s="18">
         <v>19</v>
       </c>
-      <c r="V26" s="18">
+      <c r="V27" s="18">
         <v>20</v>
       </c>
-      <c r="W26" s="18">
-        <v>0</v>
-      </c>
-      <c r="X26" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C27" s="7" t="s">
+      <c r="W27" s="18">
+        <v>0</v>
+      </c>
+      <c r="X27" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C28" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D28" s="7">
         <f>water!D14</f>
         <v>0</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E28" s="7">
         <f>glucose!D14</f>
         <v>0</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F28" s="7">
         <f>sucrose!D14</f>
         <v>0</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G28" s="7">
         <v>100</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H28" s="13">
         <v>100</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I28" s="7">
         <f>'gastic milk choc'!D14</f>
         <v>0</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J28" s="7">
         <f>'gastic milk choc arab'!D14</f>
         <v>0</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K28" s="7">
         <f>emulsie!D14</f>
         <v>0</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L28" s="7">
         <f>arabinose!D14</f>
         <v>0</v>
       </c>
-      <c r="M27" s="7">
-        <v>0</v>
-      </c>
-      <c r="N27" s="7">
-        <v>0</v>
-      </c>
-      <c r="O27" s="7">
-        <v>0</v>
-      </c>
-      <c r="P27">
+      <c r="M28" s="7">
+        <v>0</v>
+      </c>
+      <c r="N28" s="7">
+        <v>0</v>
+      </c>
+      <c r="O28" s="7">
+        <v>0</v>
+      </c>
+      <c r="P28">
         <v>50</v>
       </c>
-      <c r="Q27">
+      <c r="Q28">
         <v>100</v>
       </c>
-      <c r="R27" s="16">
+      <c r="R28" s="16">
         <v>60</v>
       </c>
-      <c r="S27" s="16">
+      <c r="S28" s="16">
         <v>100</v>
       </c>
-      <c r="T27" s="16">
-        <v>0</v>
-      </c>
-      <c r="U27" s="18">
+      <c r="T28" s="16">
+        <v>0</v>
+      </c>
+      <c r="U28" s="18">
         <v>60</v>
       </c>
-      <c r="V27" s="18">
+      <c r="V28" s="18">
         <v>100</v>
       </c>
-      <c r="W27" s="18">
-        <v>0</v>
-      </c>
-      <c r="X27" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C28" s="7" t="s">
+      <c r="W28" s="18">
+        <v>0</v>
+      </c>
+      <c r="X28" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C29" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D29" s="7">
         <f>water!D15</f>
         <v>0</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E29" s="7">
         <f>glucose!D15</f>
         <v>0</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F29" s="7">
         <f>sucrose!D15</f>
         <v>0</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G29" s="7">
         <f>'milk choc'!D15</f>
         <v>0</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H29" s="13">
         <f>'milk chocolate arabinose'!D15</f>
         <v>0</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I29" s="7">
         <f>'gastic milk choc'!D15</f>
         <v>0</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J29" s="7">
         <f>'gastic milk choc arab'!D15</f>
         <v>0</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K29" s="7">
         <f>emulsie!D15</f>
         <v>0</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L29" s="7">
         <f>arabinose!D15</f>
         <v>0</v>
       </c>
-      <c r="M28" s="7">
-        <v>0</v>
-      </c>
-      <c r="N28" s="7">
-        <v>0</v>
-      </c>
-      <c r="O28" s="7">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28" s="16">
-        <v>0</v>
-      </c>
-      <c r="S28" s="16">
-        <v>0</v>
-      </c>
-      <c r="T28" s="16">
-        <v>0</v>
-      </c>
-      <c r="U28" s="18">
+      <c r="M29" s="7">
+        <v>0</v>
+      </c>
+      <c r="N29" s="7">
+        <v>0</v>
+      </c>
+      <c r="O29" s="7">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" s="16">
+        <v>0</v>
+      </c>
+      <c r="S29" s="16">
+        <v>0</v>
+      </c>
+      <c r="T29" s="16">
+        <v>0</v>
+      </c>
+      <c r="U29" s="18">
         <v>20</v>
       </c>
-      <c r="V28" s="18">
-        <v>0</v>
-      </c>
-      <c r="W28" s="18">
-        <v>0</v>
-      </c>
-      <c r="X28" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C29" s="7" t="s">
+      <c r="V29" s="18">
+        <v>0</v>
+      </c>
+      <c r="W29" s="18">
+        <v>0</v>
+      </c>
+      <c r="X29" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C30" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D30" s="7">
         <f>water!D16</f>
         <v>0</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E30" s="7">
         <f>glucose!D16</f>
         <v>0</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F30" s="7">
         <f>sucrose!D16</f>
         <v>0</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G30" s="7">
         <f>'milk choc'!D16</f>
         <v>0</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H30" s="13">
         <f>'milk chocolate arabinose'!D16</f>
         <v>0</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I30" s="7">
         <f>'gastic milk choc'!D16</f>
         <v>0</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J30" s="7">
         <f>'gastic milk choc arab'!D16</f>
         <v>0</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K30" s="7">
         <f>emulsie!D16</f>
         <v>0</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L30" s="7">
         <f>arabinose!D16</f>
         <v>0</v>
       </c>
-      <c r="M29" s="7">
-        <v>0</v>
-      </c>
-      <c r="N29" s="7">
-        <v>0</v>
-      </c>
-      <c r="O29" s="7">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29" s="16">
+      <c r="M30" s="7">
+        <v>0</v>
+      </c>
+      <c r="N30" s="7">
+        <v>0</v>
+      </c>
+      <c r="O30" s="7">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30" s="16">
         <v>40</v>
       </c>
-      <c r="S29" s="16">
-        <v>0</v>
-      </c>
-      <c r="T29" s="16">
-        <v>0</v>
-      </c>
-      <c r="U29" s="18">
+      <c r="S30" s="16">
+        <v>0</v>
+      </c>
+      <c r="T30" s="16">
+        <v>0</v>
+      </c>
+      <c r="U30" s="18">
         <v>40</v>
       </c>
-      <c r="V29" s="18">
-        <v>0</v>
-      </c>
-      <c r="W29" s="18">
-        <v>0</v>
-      </c>
-      <c r="X29" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="V30" s="18">
+        <v>0</v>
+      </c>
+      <c r="W30" s="18">
+        <v>0</v>
+      </c>
+      <c r="X30" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31" s="1">
         <v>0.1</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E31" s="1">
         <v>0.1</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F31" s="1">
         <v>0.1</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G31" s="1">
         <v>1</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H31" s="15">
         <v>1</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I31" s="1">
         <v>1</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J31" s="1">
         <v>1</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K31" s="1">
         <f>emulsie!D17</f>
         <v>1</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L31" s="1">
         <v>0.1</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M31" s="1">
         <v>2</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N31" s="1">
         <v>10</v>
       </c>
-      <c r="O30" s="1">
+      <c r="O31" s="1">
         <v>1</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P31" s="1">
         <v>10</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q31" s="1">
         <v>100</v>
       </c>
-      <c r="R30" s="17">
+      <c r="R31" s="17">
         <v>5</v>
       </c>
-      <c r="S30" s="17">
+      <c r="S31" s="17">
         <v>1</v>
       </c>
-      <c r="T30" s="17">
+      <c r="T31" s="17">
         <v>1</v>
       </c>
-      <c r="U30" s="19">
+      <c r="U31" s="19">
         <v>10</v>
       </c>
-      <c r="V30" s="19">
+      <c r="V31" s="19">
         <v>20</v>
       </c>
-      <c r="W30" s="19">
+      <c r="W31" s="19">
         <v>20</v>
       </c>
-      <c r="X30" s="1">
+      <c r="X31" s="1">
         <v>0.1</v>
       </c>
-      <c r="Y30" s="1">
+      <c r="Y31" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z30" s="1">
+      <c r="Z31" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA30" s="1">
+      <c r="AA31" s="1">
         <v>0.1</v>
       </c>
-      <c r="AB30" s="1">
+      <c r="AB31" s="1">
         <v>1</v>
       </c>
-      <c r="AC30" s="1">
+      <c r="AC31" s="1">
         <v>1</v>
       </c>
-      <c r="AD30" s="1">
+      <c r="AD31" s="1">
         <v>1</v>
       </c>
-      <c r="AE30" s="1">
+      <c r="AE31" s="1">
         <v>1</v>
       </c>
-      <c r="AF30" s="1">
+      <c r="AF31" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C31" s="7" t="s">
+      <c r="AG31" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C32" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D32" s="7">
         <f>water!D18</f>
         <v>0</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E32" s="7">
         <f>glucose!D18</f>
         <v>0</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F32" s="7">
         <f>sucrose!D18</f>
         <v>0</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G32" s="7">
         <v>6</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H32" s="13">
         <v>7</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I32" s="7">
         <f>'gastic milk choc'!D18</f>
         <v>0</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J32" s="7">
         <f>'gastic milk choc arab'!D18</f>
         <v>0</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K32" s="7">
         <f>emulsie!D18</f>
         <v>0</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L32" s="7">
         <f>arabinose!D18</f>
         <v>0</v>
       </c>
-      <c r="M31" s="7">
-        <v>0</v>
-      </c>
-      <c r="N31" s="7">
-        <v>0</v>
-      </c>
-      <c r="O31" s="7">
-        <v>0</v>
-      </c>
-      <c r="P31">
+      <c r="M32" s="7">
+        <v>0</v>
+      </c>
+      <c r="N32" s="7">
+        <v>0</v>
+      </c>
+      <c r="O32" s="7">
+        <v>0</v>
+      </c>
+      <c r="P32">
         <v>10</v>
       </c>
-      <c r="Q31">
+      <c r="Q32">
         <v>11</v>
       </c>
-      <c r="R31" s="16">
+      <c r="R32" s="16">
         <v>16</v>
       </c>
-      <c r="S31" s="16">
+      <c r="S32" s="16">
         <v>17</v>
       </c>
-      <c r="T31" s="16">
-        <v>0</v>
-      </c>
-      <c r="U31" s="18">
+      <c r="T32" s="16">
+        <v>0</v>
+      </c>
+      <c r="U32" s="18">
         <v>19</v>
       </c>
-      <c r="V31" s="18">
+      <c r="V32" s="18">
         <v>20</v>
       </c>
-      <c r="W31" s="18">
-        <v>0</v>
-      </c>
-      <c r="X31" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C32" s="7" t="s">
+      <c r="W32" s="18">
+        <v>0</v>
+      </c>
+      <c r="X32" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D33" s="7">
         <f>water!D19</f>
         <v>0</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E33" s="7">
         <f>glucose!D19</f>
         <v>0</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F33" s="7">
         <f>sucrose!D19</f>
         <v>0</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G33" s="7">
         <v>100</v>
       </c>
-      <c r="H32" s="13">
+      <c r="H33" s="13">
         <v>100</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I33" s="7">
         <f>'gastic milk choc'!D19</f>
         <v>0</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J33" s="7">
         <f>'gastic milk choc arab'!D19</f>
         <v>0</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K33" s="7">
         <f>emulsie!D19</f>
         <v>0</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L33" s="7">
         <f>arabinose!D19</f>
         <v>0</v>
       </c>
-      <c r="M32" s="7">
-        <v>0</v>
-      </c>
-      <c r="N32" s="7">
-        <v>0</v>
-      </c>
-      <c r="O32" s="7">
-        <v>0</v>
-      </c>
-      <c r="P32">
+      <c r="M33" s="7">
+        <v>0</v>
+      </c>
+      <c r="N33" s="7">
+        <v>0</v>
+      </c>
+      <c r="O33" s="7">
+        <v>0</v>
+      </c>
+      <c r="P33">
         <v>50</v>
       </c>
-      <c r="Q32">
+      <c r="Q33">
         <v>100</v>
       </c>
-      <c r="R32" s="16">
+      <c r="R33" s="16">
         <v>50</v>
       </c>
-      <c r="S32" s="16">
+      <c r="S33" s="16">
         <v>100</v>
       </c>
-      <c r="T32" s="16">
-        <v>0</v>
-      </c>
-      <c r="U32" s="18">
+      <c r="T33" s="16">
+        <v>0</v>
+      </c>
+      <c r="U33" s="18">
         <v>50</v>
       </c>
-      <c r="V32" s="18">
+      <c r="V33" s="18">
         <v>100</v>
       </c>
-      <c r="W32" s="18">
-        <v>0</v>
-      </c>
-      <c r="X32" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C33" s="7" t="s">
+      <c r="W33" s="18">
+        <v>0</v>
+      </c>
+      <c r="X33" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C34" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D34" s="7">
         <f>water!D20</f>
         <v>0</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E34" s="7">
         <f>glucose!D20</f>
         <v>0</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F34" s="7">
         <f>sucrose!D20</f>
         <v>0</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G34" s="7">
         <f>'milk choc'!D20</f>
         <v>0</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H34" s="13">
         <f>'milk chocolate arabinose'!D20</f>
         <v>0</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I34" s="7">
         <f>'gastic milk choc'!D20</f>
         <v>0</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J34" s="7">
         <f>'gastic milk choc arab'!D20</f>
         <v>0</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K34" s="7">
         <f>emulsie!D20</f>
         <v>0</v>
       </c>
-      <c r="L33" s="7">
+      <c r="L34" s="7">
         <f>arabinose!D20</f>
         <v>0</v>
       </c>
-      <c r="M33" s="7">
-        <v>0</v>
-      </c>
-      <c r="N33" s="7">
-        <v>0</v>
-      </c>
-      <c r="O33" s="7">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33" s="16">
-        <v>0</v>
-      </c>
-      <c r="S33" s="16">
-        <v>0</v>
-      </c>
-      <c r="T33" s="16">
-        <v>0</v>
-      </c>
-      <c r="U33" s="18">
+      <c r="M34" s="7">
+        <v>0</v>
+      </c>
+      <c r="N34" s="7">
+        <v>0</v>
+      </c>
+      <c r="O34" s="7">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34" s="16">
+        <v>0</v>
+      </c>
+      <c r="S34" s="16">
+        <v>0</v>
+      </c>
+      <c r="T34" s="16">
+        <v>0</v>
+      </c>
+      <c r="U34" s="18">
         <v>20</v>
       </c>
-      <c r="V33" s="18">
-        <v>0</v>
-      </c>
-      <c r="W33" s="18">
-        <v>0</v>
-      </c>
-      <c r="X33" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="C34" s="7" t="s">
+      <c r="V34" s="18">
+        <v>0</v>
+      </c>
+      <c r="W34" s="18">
+        <v>0</v>
+      </c>
+      <c r="X34" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C35" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D35" s="7">
         <f>water!D21</f>
         <v>0</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E35" s="7">
         <f>glucose!D21</f>
         <v>0</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F35" s="7">
         <f>sucrose!D21</f>
         <v>0</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G35" s="7">
         <f>'milk choc'!D21</f>
         <v>0</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H35" s="13">
         <f>'milk chocolate arabinose'!D21</f>
         <v>0</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I35" s="7">
         <f>'gastic milk choc'!D21</f>
         <v>0</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J35" s="7">
         <f>'gastic milk choc arab'!D21</f>
         <v>0</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K35" s="7">
         <f>emulsie!D21</f>
         <v>0</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L35" s="7">
         <f>arabinose!D21</f>
         <v>0</v>
       </c>
-      <c r="M34" s="7">
-        <v>0</v>
-      </c>
-      <c r="N34" s="7">
-        <v>0</v>
-      </c>
-      <c r="O34" s="7">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34" s="16">
+      <c r="M35" s="7">
+        <v>0</v>
+      </c>
+      <c r="N35" s="7">
+        <v>0</v>
+      </c>
+      <c r="O35" s="7">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35" s="16">
         <v>50</v>
       </c>
-      <c r="S34" s="16">
-        <v>0</v>
-      </c>
-      <c r="T34" s="16">
-        <v>0</v>
-      </c>
-      <c r="U34" s="18">
+      <c r="S35" s="16">
+        <v>0</v>
+      </c>
+      <c r="T35" s="16">
+        <v>0</v>
+      </c>
+      <c r="U35" s="18">
         <v>50</v>
       </c>
-      <c r="V34" s="18">
-        <v>0</v>
-      </c>
-      <c r="W34" s="18">
-        <v>0</v>
-      </c>
-      <c r="X34" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="H35" s="13"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
+      <c r="V35" s="18">
+        <v>0</v>
+      </c>
+      <c r="W35" s="18">
+        <v>0</v>
+      </c>
+      <c r="X35" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="H36" s="13"/>
       <c r="P36"/>
       <c r="Q36"/>
@@ -3207,10 +3289,8 @@
       <c r="V36"/>
       <c r="W36"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B37" s="8" t="s">
-        <v>26</v>
-      </c>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="H37" s="13"/>
       <c r="P37"/>
@@ -3221,584 +3301,503 @@
       <c r="V37"/>
       <c r="W37"/>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B38" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="H38" s="13"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="S38"/>
+      <c r="T38"/>
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A39" s="7">
         <v>1</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B39" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D39" s="7">
         <f>water!D25</f>
         <v>100</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E39" s="7">
         <f>glucose!D25</f>
         <v>0</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F39" s="7">
         <f>sucrose!D25</f>
         <v>0</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G39" s="7">
         <f>'milk choc'!D25</f>
         <v>0</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H39" s="13">
         <f>'milk chocolate arabinose'!D25</f>
         <v>0</v>
       </c>
-      <c r="I38" s="7">
+      <c r="I39" s="7">
         <f>'gastic milk choc'!D25</f>
         <v>36.94</v>
       </c>
-      <c r="J38" s="7">
+      <c r="J39" s="7">
         <f>'gastic milk choc arab'!D25</f>
         <v>36.94</v>
       </c>
-      <c r="K38" s="7">
+      <c r="K39" s="7">
         <f>emulsie!D25</f>
         <v>50</v>
       </c>
-      <c r="L38" s="7">
+      <c r="L39" s="7">
         <f>arabinose!D25</f>
         <v>0</v>
       </c>
-      <c r="M38" s="7">
-        <v>0</v>
-      </c>
-      <c r="N38" s="7">
-        <v>0</v>
-      </c>
-      <c r="O38" s="7">
-        <v>0</v>
-      </c>
-      <c r="P38">
+      <c r="M39" s="7">
+        <v>0</v>
+      </c>
+      <c r="N39" s="7">
+        <v>0</v>
+      </c>
+      <c r="O39" s="7">
+        <v>0</v>
+      </c>
+      <c r="P39">
         <v>14</v>
       </c>
-      <c r="Q38">
+      <c r="Q39">
         <v>14</v>
       </c>
-      <c r="R38" s="7">
+      <c r="R39" s="7">
         <v>67</v>
       </c>
-      <c r="S38">
+      <c r="S39">
         <v>67</v>
       </c>
-      <c r="T38">
+      <c r="T39">
         <v>67</v>
       </c>
-      <c r="U38">
+      <c r="U39">
         <v>54</v>
       </c>
-      <c r="V38">
+      <c r="V39">
         <v>54</v>
       </c>
-      <c r="W38">
+      <c r="W39">
         <v>54</v>
       </c>
-      <c r="X38" s="7">
+      <c r="X39" s="7">
         <v>100</v>
       </c>
-      <c r="Y38" s="7">
+      <c r="Y39" s="7">
         <v>100</v>
       </c>
-      <c r="Z38" s="7">
+      <c r="Z39" s="7">
         <v>100</v>
       </c>
-      <c r="AA38" s="7">
+      <c r="AA39" s="7">
         <v>100</v>
       </c>
-      <c r="AB38" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A39" s="7">
+      <c r="AB39" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A40" s="7">
         <v>2</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D40" s="7">
         <f>water!D26</f>
         <v>0</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E40" s="7">
         <f>glucose!D26</f>
         <v>0</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F40" s="7">
         <f>sucrose!D26</f>
         <v>0</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G40" s="7">
         <f>'milk choc'!D26</f>
         <v>32.729999999999997</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H40" s="13">
         <f>'milk chocolate arabinose'!D26</f>
         <v>32.729999999999997</v>
       </c>
-      <c r="I39" s="7">
+      <c r="I40" s="7">
         <f>'gastic milk choc'!D26</f>
         <v>29.13</v>
       </c>
-      <c r="J39" s="7">
+      <c r="J40" s="7">
         <f>'gastic milk choc arab'!D26</f>
         <v>29.13</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K40" s="7">
         <f>emulsie!D26</f>
         <v>50</v>
       </c>
-      <c r="L39" s="7">
+      <c r="L40" s="7">
         <f>arabinose!D26</f>
         <v>0</v>
       </c>
-      <c r="M39" s="7">
-        <v>0</v>
-      </c>
-      <c r="N39" s="7">
-        <v>0</v>
-      </c>
-      <c r="O39" s="7">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39" s="7">
+      <c r="M40" s="7">
+        <v>0</v>
+      </c>
+      <c r="N40" s="7">
+        <v>0</v>
+      </c>
+      <c r="O40" s="7">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7">
         <v>9</v>
       </c>
-      <c r="S39">
+      <c r="S40">
         <v>9</v>
       </c>
-      <c r="T39">
+      <c r="T40">
         <v>9</v>
       </c>
-      <c r="U39">
+      <c r="U40">
         <v>9</v>
       </c>
-      <c r="V39">
+      <c r="V40">
         <v>9</v>
       </c>
-      <c r="W39">
+      <c r="W40">
         <v>9</v>
       </c>
-      <c r="X39" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A40" s="7">
+      <c r="X40" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A41" s="7">
         <v>3</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B41" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="7">
-        <f>water!D27</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="7">
-        <v>99</v>
-      </c>
-      <c r="F40" s="7">
-        <f>sucrose!D27</f>
-        <v>0</v>
-      </c>
-      <c r="G40" s="7">
-        <f>'milk choc'!D27</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="13">
-        <f>'milk chocolate arabinose'!D27</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="7">
-        <f>'gastic milk choc'!D27</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="7">
-        <f>'gastic milk choc arab'!D27</f>
-        <v>0</v>
-      </c>
-      <c r="K40" s="7">
-        <f>emulsie!D27</f>
-        <v>0</v>
-      </c>
-      <c r="L40" s="7">
-        <f>arabinose!D27</f>
-        <v>0</v>
-      </c>
-      <c r="M40" s="7">
-        <v>0</v>
-      </c>
-      <c r="N40" s="7">
-        <v>0</v>
-      </c>
-      <c r="O40" s="7">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40" s="7">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A41" s="7">
-        <v>4</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>9</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="7">
+        <f>water!D27</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="7">
+        <v>99</v>
+      </c>
+      <c r="F41" s="7">
+        <f>sucrose!D27</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="7">
+        <f>'milk choc'!D27</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="13">
+        <f>'milk chocolate arabinose'!D27</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="7">
+        <f>'gastic milk choc'!D27</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="7">
+        <f>'gastic milk choc arab'!D27</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="7">
+        <f>emulsie!D27</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="7">
+        <f>arabinose!D27</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="7">
+        <v>0</v>
+      </c>
+      <c r="N41" s="7">
+        <v>0</v>
+      </c>
+      <c r="O41" s="7">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41" s="7">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A42" s="7">
+        <v>4</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="7">
         <f>water!D28</f>
         <v>0</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E42" s="7">
         <f>glucose!D28</f>
         <v>0</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F42" s="7">
         <f>sucrose!D28</f>
         <v>0</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G42" s="7">
         <f>'milk choc'!D28</f>
         <v>1.08</v>
       </c>
-      <c r="H41" s="13">
+      <c r="H42" s="13">
         <f>'milk chocolate arabinose'!D28</f>
         <v>1.08</v>
       </c>
-      <c r="I41" s="7">
+      <c r="I42" s="7">
         <f>'gastic milk choc'!D28</f>
         <v>1.08</v>
       </c>
-      <c r="J41" s="7">
+      <c r="J42" s="7">
         <f>'gastic milk choc arab'!D28</f>
         <v>1.08</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K42" s="7">
         <f>emulsie!D28</f>
         <v>0</v>
       </c>
-      <c r="L41" s="7">
+      <c r="L42" s="7">
         <f>arabinose!D28</f>
         <v>0</v>
       </c>
-      <c r="M41" s="7">
-        <v>0</v>
-      </c>
-      <c r="N41" s="7">
-        <v>0</v>
-      </c>
-      <c r="O41" s="7">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41" s="7">
+      <c r="M42" s="7">
+        <v>0</v>
+      </c>
+      <c r="N42" s="7">
+        <v>0</v>
+      </c>
+      <c r="O42" s="7">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42" s="7">
         <v>6</v>
       </c>
-      <c r="S41">
+      <c r="S42">
         <v>6</v>
       </c>
-      <c r="T41">
+      <c r="T42">
         <v>6</v>
       </c>
-      <c r="U41">
+      <c r="U42">
         <v>6</v>
       </c>
-      <c r="V41">
+      <c r="V42">
         <v>6</v>
       </c>
-      <c r="W41">
+      <c r="W42">
         <v>6</v>
       </c>
-      <c r="X41" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A42" s="7">
+      <c r="X42" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A43" s="7">
         <v>5</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B43" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="7">
-        <f>water!D29</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="7">
-        <f>glucose!D29</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="7">
-        <f>sucrose!D29</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="7">
-        <f>'milk choc'!D29</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="13">
-        <f>'milk chocolate arabinose'!D29</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="7">
-        <f>'gastic milk choc'!D29</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="7">
-        <f>'gastic milk choc arab'!D29</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="7">
-        <f>emulsie!D29</f>
-        <v>0</v>
-      </c>
-      <c r="L42" s="7">
-        <f>arabinose!D29</f>
-        <v>0</v>
-      </c>
-      <c r="M42" s="7">
-        <v>0</v>
-      </c>
-      <c r="N42" s="7">
-        <v>0</v>
-      </c>
-      <c r="O42" s="7">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42" s="7">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A43" s="7">
-        <v>6</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D43" s="7">
-        <f>water!D30</f>
+        <f>water!D29</f>
         <v>0</v>
       </c>
       <c r="E43" s="7">
-        <f>glucose!D30</f>
+        <f>glucose!D29</f>
         <v>0</v>
       </c>
       <c r="F43" s="7">
-        <f>sucrose!D30</f>
+        <f>sucrose!D29</f>
         <v>0</v>
       </c>
       <c r="G43" s="7">
-        <f>'milk choc'!D30</f>
+        <f>'milk choc'!D29</f>
         <v>0</v>
       </c>
       <c r="H43" s="13">
-        <f>'milk chocolate arabinose'!D30</f>
+        <f>'milk chocolate arabinose'!D29</f>
         <v>0</v>
       </c>
       <c r="I43" s="7">
-        <f>'gastic milk choc'!D30</f>
+        <f>'gastic milk choc'!D29</f>
         <v>0</v>
       </c>
       <c r="J43" s="7">
-        <f>'gastic milk choc arab'!D30</f>
+        <f>'gastic milk choc arab'!D29</f>
         <v>0</v>
       </c>
       <c r="K43" s="7">
-        <f>emulsie!D30</f>
+        <f>emulsie!D29</f>
         <v>0</v>
       </c>
       <c r="L43" s="7">
-        <f>arabinose!D30</f>
+        <f>arabinose!D29</f>
         <v>0</v>
       </c>
       <c r="M43" s="7">
@@ -3861,55 +3860,58 @@
       <c r="AF43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="7">
-        <f>water!D31</f>
+        <f>water!D30</f>
         <v>0</v>
       </c>
       <c r="E44" s="7">
-        <f>glucose!D31</f>
+        <f>glucose!D30</f>
         <v>0</v>
       </c>
       <c r="F44" s="7">
-        <f>sucrose!D31</f>
+        <f>sucrose!D30</f>
         <v>0</v>
       </c>
       <c r="G44" s="7">
-        <f>'milk choc'!D31</f>
+        <f>'milk choc'!D30</f>
         <v>0</v>
       </c>
       <c r="H44" s="13">
-        <f>'milk chocolate arabinose'!D31</f>
+        <f>'milk chocolate arabinose'!D30</f>
         <v>0</v>
       </c>
       <c r="I44" s="7">
-        <f>'gastic milk choc'!D31</f>
+        <f>'gastic milk choc'!D30</f>
         <v>0</v>
       </c>
       <c r="J44" s="7">
-        <f>'gastic milk choc arab'!D31</f>
+        <f>'gastic milk choc arab'!D30</f>
         <v>0</v>
       </c>
       <c r="K44" s="7">
-        <f>emulsie!D31</f>
+        <f>emulsie!D30</f>
         <v>0</v>
       </c>
       <c r="L44" s="7">
-        <f>arabinose!D31</f>
+        <f>arabinose!D30</f>
         <v>0</v>
       </c>
       <c r="M44" s="7">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="N44" s="7">
         <v>0</v>
@@ -3918,28 +3920,28 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q44">
         <v>0</v>
       </c>
       <c r="R44" s="7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X44" s="7">
         <v>0</v>
@@ -3968,85 +3970,88 @@
       <c r="AF44" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="7">
-        <f>water!D32</f>
+        <f>water!D31</f>
         <v>0</v>
       </c>
       <c r="E45" s="7">
-        <f>glucose!D32</f>
+        <f>glucose!D31</f>
         <v>0</v>
       </c>
       <c r="F45" s="7">
-        <f>sucrose!D32</f>
+        <f>sucrose!D31</f>
         <v>0</v>
       </c>
       <c r="G45" s="7">
-        <f>'milk choc'!D32</f>
+        <f>'milk choc'!D31</f>
         <v>0</v>
       </c>
       <c r="H45" s="13">
-        <f>'milk chocolate arabinose'!D32</f>
+        <f>'milk chocolate arabinose'!D31</f>
         <v>0</v>
       </c>
       <c r="I45" s="7">
-        <f>'gastic milk choc'!D32</f>
+        <f>'gastic milk choc'!D31</f>
         <v>0</v>
       </c>
       <c r="J45" s="7">
-        <f>'gastic milk choc arab'!D32</f>
+        <f>'gastic milk choc arab'!D31</f>
         <v>0</v>
       </c>
       <c r="K45" s="7">
-        <f>emulsie!D32</f>
+        <f>emulsie!D31</f>
         <v>0</v>
       </c>
       <c r="L45" s="7">
-        <f>arabinose!D32</f>
+        <f>arabinose!D31</f>
         <v>0</v>
       </c>
       <c r="M45" s="7">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="N45" s="7">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O45" s="7">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q45">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R45" s="7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X45" s="7">
         <v>0</v>
@@ -4075,260 +4080,274 @@
       <c r="AF45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D46" s="7">
+        <f>water!D32</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="7">
+        <f>glucose!D32</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="7">
+        <f>sucrose!D32</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="7">
+        <f>'milk choc'!D32</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="13">
+        <f>'milk chocolate arabinose'!D32</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="7">
+        <f>'gastic milk choc'!D32</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="7">
+        <f>'gastic milk choc arab'!D32</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="7">
+        <f>emulsie!D32</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="7">
+        <f>arabinose!D32</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="7">
+        <v>0</v>
+      </c>
+      <c r="N46" s="7">
+        <v>99</v>
+      </c>
+      <c r="O46" s="7">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>75</v>
+      </c>
+      <c r="R46" s="7">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A47" s="7">
+        <v>12</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="7">
         <f>water!D33</f>
         <v>0</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E47" s="7">
         <f>glucose!D33</f>
         <v>0</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F47" s="7">
         <f>sucrose!D33</f>
         <v>0</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G47" s="7">
         <f>'milk choc'!D33</f>
         <v>6</v>
       </c>
-      <c r="H46" s="13">
+      <c r="H47" s="13">
         <f>'milk chocolate arabinose'!D33</f>
         <v>6</v>
       </c>
-      <c r="I46" s="7">
+      <c r="I47" s="7">
         <f>'gastic milk choc'!D33</f>
         <v>1.78</v>
       </c>
-      <c r="J46" s="7">
+      <c r="J47" s="7">
         <f>'gastic milk choc arab'!D33</f>
         <v>1.78</v>
       </c>
-      <c r="K46" s="7">
+      <c r="K47" s="7">
         <f>emulsie!D33</f>
         <v>0</v>
       </c>
-      <c r="L46" s="7">
+      <c r="L47" s="7">
         <f>arabinose!D33</f>
         <v>0</v>
       </c>
-      <c r="M46" s="7">
-        <v>0</v>
-      </c>
-      <c r="N46" s="7">
-        <v>0</v>
-      </c>
-      <c r="O46" s="7">
+      <c r="M47" s="7">
+        <v>0</v>
+      </c>
+      <c r="N47" s="7">
+        <v>0</v>
+      </c>
+      <c r="O47" s="7">
         <v>99</v>
       </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46" s="7">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47" s="7">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A48" s="7">
         <v>20</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B48" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="7">
-        <f>water!D34</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="7">
-        <f>glucose!D34</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="7">
-        <f>sucrose!D34</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="7">
-        <f>'milk choc'!D34</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="13">
-        <f>'milk chocolate arabinose'!D34</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="7">
-        <f>'gastic milk choc'!D34</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="7">
-        <f>'gastic milk choc arab'!D34</f>
-        <v>0</v>
-      </c>
-      <c r="K47" s="7">
-        <f>emulsie!D34</f>
-        <v>0</v>
-      </c>
-      <c r="L47" s="7">
-        <f>arabinose!D34</f>
-        <v>0</v>
-      </c>
-      <c r="M47" s="7">
-        <v>0</v>
-      </c>
-      <c r="N47" s="7">
-        <v>0</v>
-      </c>
-      <c r="O47" s="7">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47" s="7">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
-        <v>21</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>4</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="7">
-        <f>water!D35</f>
+        <f>water!D34</f>
         <v>0</v>
       </c>
       <c r="E48" s="7">
-        <f>glucose!D35</f>
+        <f>glucose!D34</f>
         <v>0</v>
       </c>
       <c r="F48" s="7">
-        <v>98</v>
+        <f>sucrose!D34</f>
+        <v>0</v>
       </c>
       <c r="G48" s="7">
-        <v>40.5</v>
+        <f>'milk choc'!D34</f>
+        <v>0</v>
       </c>
       <c r="H48" s="13">
-        <v>28.7</v>
+        <f>'milk chocolate arabinose'!D34</f>
+        <v>0</v>
       </c>
       <c r="I48" s="7">
-        <v>19</v>
+        <f>'gastic milk choc'!D34</f>
+        <v>0</v>
       </c>
       <c r="J48" s="7">
-        <v>14</v>
+        <f>'gastic milk choc arab'!D34</f>
+        <v>0</v>
       </c>
       <c r="K48" s="7">
-        <f>emulsie!D35</f>
+        <f>emulsie!D34</f>
         <v>0</v>
       </c>
       <c r="L48" s="7">
-        <f>arabinose!D35</f>
+        <f>arabinose!D34</f>
         <v>0</v>
       </c>
       <c r="M48" s="7">
@@ -4341,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="P48">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R48" s="7">
         <v>0</v>
@@ -4391,51 +4410,49 @@
       <c r="AF48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D49" s="7">
-        <f>water!D36</f>
+        <f>water!D35</f>
         <v>0</v>
       </c>
       <c r="E49" s="7">
-        <f>glucose!D36</f>
+        <f>glucose!D35</f>
         <v>0</v>
       </c>
       <c r="F49" s="7">
-        <f>sucrose!D36</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G49" s="7">
-        <f>'milk choc'!D36</f>
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="H49" s="13">
-        <f>'milk chocolate arabinose'!D36</f>
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="I49" s="7">
-        <f>'gastic milk choc'!D36</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J49" s="7">
-        <f>'gastic milk choc arab'!D36</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K49" s="7">
-        <f>emulsie!D36</f>
+        <f>emulsie!D35</f>
         <v>0</v>
       </c>
       <c r="L49" s="7">
-        <f>arabinose!D36</f>
+        <f>arabinose!D35</f>
         <v>0</v>
       </c>
       <c r="M49" s="7">
@@ -4448,10 +4465,10 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R49" s="7">
         <v>0</v>
@@ -4498,51 +4515,54 @@
       <c r="AF49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D50" s="7">
-        <f>water!D37</f>
+        <f>water!D36</f>
         <v>0</v>
       </c>
       <c r="E50" s="7">
-        <f>glucose!D37</f>
+        <f>glucose!D36</f>
         <v>0</v>
       </c>
       <c r="F50" s="7">
-        <f>sucrose!D37</f>
+        <f>sucrose!D36</f>
         <v>0</v>
       </c>
       <c r="G50" s="7">
-        <f>'milk choc'!D37</f>
+        <f>'milk choc'!D36</f>
         <v>0</v>
       </c>
       <c r="H50" s="13">
-        <f>'milk chocolate arabinose'!D37</f>
+        <f>'milk chocolate arabinose'!D36</f>
         <v>0</v>
       </c>
       <c r="I50" s="7">
-        <f>'gastic milk choc'!D37</f>
+        <f>'gastic milk choc'!D36</f>
         <v>0</v>
       </c>
       <c r="J50" s="7">
-        <f>'gastic milk choc arab'!D37</f>
+        <f>'gastic milk choc arab'!D36</f>
         <v>0</v>
       </c>
       <c r="K50" s="7">
-        <f>emulsie!D37</f>
+        <f>emulsie!D36</f>
         <v>0</v>
       </c>
       <c r="L50" s="7">
-        <f>arabinose!D37</f>
+        <f>arabinose!D36</f>
         <v>0</v>
       </c>
       <c r="M50" s="7">
@@ -4605,42 +4625,54 @@
       <c r="AF50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D51" s="7">
+        <f>water!D37</f>
         <v>0</v>
       </c>
       <c r="E51" s="7">
+        <f>glucose!D37</f>
         <v>0</v>
       </c>
       <c r="F51" s="7">
+        <f>sucrose!D37</f>
         <v>0</v>
       </c>
       <c r="G51" s="7">
+        <f>'milk choc'!D37</f>
         <v>0</v>
       </c>
       <c r="H51" s="13">
+        <f>'milk chocolate arabinose'!D37</f>
         <v>0</v>
       </c>
       <c r="I51" s="7">
+        <f>'gastic milk choc'!D37</f>
         <v>0</v>
       </c>
       <c r="J51" s="7">
+        <f>'gastic milk choc arab'!D37</f>
         <v>0</v>
       </c>
       <c r="K51" s="7">
+        <f>emulsie!D37</f>
         <v>0</v>
       </c>
       <c r="L51" s="7">
+        <f>arabinose!D37</f>
         <v>0</v>
       </c>
       <c r="M51" s="7">
@@ -4703,265 +4735,265 @@
       <c r="AF51" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D52" s="7">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>0</v>
+      </c>
+      <c r="H52" s="13">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7">
+        <v>0</v>
+      </c>
+      <c r="K52" s="7">
+        <v>0</v>
+      </c>
+      <c r="L52" s="7">
+        <v>0</v>
+      </c>
+      <c r="M52" s="7">
+        <v>0</v>
+      </c>
+      <c r="N52" s="7">
+        <v>0</v>
+      </c>
+      <c r="O52" s="7">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A53" s="7">
+        <v>25</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="7">
         <f>water!D38</f>
         <v>0</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E53" s="7">
         <f>glucose!D38</f>
         <v>0</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F53" s="7">
         <f>sucrose!D38</f>
         <v>0</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G53" s="7">
         <f>'milk choc'!D38</f>
         <v>0</v>
       </c>
-      <c r="H52" s="13">
+      <c r="H53" s="13">
         <f>'milk chocolate arabinose'!D38</f>
         <v>11.9</v>
       </c>
-      <c r="I52" s="7">
+      <c r="I53" s="7">
         <f>'gastic milk choc'!D38</f>
         <v>0</v>
       </c>
-      <c r="J52" s="7">
+      <c r="J53" s="7">
         <f>'gastic milk choc arab'!D38</f>
         <v>5</v>
       </c>
-      <c r="K52" s="7">
+      <c r="K53" s="7">
         <f>emulsie!D38</f>
         <v>0</v>
       </c>
-      <c r="L52" s="7">
+      <c r="L53" s="7">
         <f>arabinose!D38</f>
         <v>100</v>
       </c>
-      <c r="M52" s="7">
-        <v>0</v>
-      </c>
-      <c r="N52" s="7">
-        <v>0</v>
-      </c>
-      <c r="O52" s="7">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52" s="7">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
-      <c r="V52">
-        <v>0</v>
-      </c>
-      <c r="W52">
-        <v>0</v>
-      </c>
-      <c r="X52" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
+      <c r="M53" s="7">
+        <v>0</v>
+      </c>
+      <c r="N53" s="7">
+        <v>0</v>
+      </c>
+      <c r="O53" s="7">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53" s="7">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A54" s="7">
         <v>26</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B54" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="7">
-        <f>water!D39</f>
-        <v>0</v>
-      </c>
-      <c r="E53" s="7">
-        <f>glucose!D39</f>
-        <v>0</v>
-      </c>
-      <c r="F53" s="7">
-        <f>sucrose!D39</f>
-        <v>0</v>
-      </c>
-      <c r="G53" s="7">
-        <f>'milk choc'!D39</f>
-        <v>0</v>
-      </c>
-      <c r="H53" s="13">
-        <f>'milk chocolate arabinose'!D39</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="7">
-        <f>'gastic milk choc'!D39</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="7">
-        <f>'gastic milk choc arab'!D39</f>
-        <v>0</v>
-      </c>
-      <c r="K53" s="7">
-        <f>emulsie!D39</f>
-        <v>0</v>
-      </c>
-      <c r="L53" s="7">
-        <f>arabinose!D39</f>
-        <v>0</v>
-      </c>
-      <c r="M53" s="7">
-        <v>0</v>
-      </c>
-      <c r="N53" s="7">
-        <v>0</v>
-      </c>
-      <c r="O53" s="7">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>0</v>
-      </c>
-      <c r="R53" s="7">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>0</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>0</v>
-      </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-      <c r="X53" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A54" s="7">
-        <v>27</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D54" s="7">
-        <f>water!D40</f>
+        <f>water!D39</f>
         <v>0</v>
       </c>
       <c r="E54" s="7">
-        <f>glucose!D40</f>
+        <f>glucose!D39</f>
         <v>0</v>
       </c>
       <c r="F54" s="7">
-        <f>sucrose!D40</f>
+        <f>sucrose!D39</f>
         <v>0</v>
       </c>
       <c r="G54" s="7">
-        <f>'milk choc'!D40</f>
+        <f>'milk choc'!D39</f>
         <v>0</v>
       </c>
       <c r="H54" s="13">
-        <f>'milk chocolate arabinose'!D40</f>
+        <f>'milk chocolate arabinose'!D39</f>
         <v>0</v>
       </c>
       <c r="I54" s="7">
-        <f>'gastic milk choc'!D40</f>
+        <f>'gastic milk choc'!D39</f>
         <v>0</v>
       </c>
       <c r="J54" s="7">
-        <f>'gastic milk choc arab'!D40</f>
+        <f>'gastic milk choc arab'!D39</f>
         <v>0</v>
       </c>
       <c r="K54" s="7">
-        <f>emulsie!D40</f>
+        <f>emulsie!D39</f>
         <v>0</v>
       </c>
       <c r="L54" s="7">
-        <f>arabinose!D40</f>
+        <f>arabinose!D39</f>
         <v>0</v>
       </c>
       <c r="M54" s="7">
@@ -5024,42 +5056,54 @@
       <c r="AF54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D55" s="7">
+        <f>water!D40</f>
         <v>0</v>
       </c>
       <c r="E55" s="7">
-        <v>1</v>
+        <f>glucose!D40</f>
+        <v>0</v>
       </c>
       <c r="F55" s="7">
+        <f>sucrose!D40</f>
         <v>0</v>
       </c>
       <c r="G55" s="7">
+        <f>'milk choc'!D40</f>
         <v>0</v>
       </c>
       <c r="H55" s="13">
+        <f>'milk chocolate arabinose'!D40</f>
         <v>0</v>
       </c>
       <c r="I55" s="7">
+        <f>'gastic milk choc'!D40</f>
         <v>0</v>
       </c>
       <c r="J55" s="7">
+        <f>'gastic milk choc arab'!D40</f>
         <v>0</v>
       </c>
       <c r="K55" s="7">
+        <f>emulsie!D40</f>
         <v>0</v>
       </c>
       <c r="L55" s="7">
+        <f>arabinose!D40</f>
         <v>0</v>
       </c>
       <c r="M55" s="7">
@@ -5122,13 +5166,16 @@
       <c r="AF55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>28</v>
@@ -5137,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="E56" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="7">
         <v>0</v>
@@ -5220,13 +5267,16 @@
       <c r="AF56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>28</v>
@@ -5238,19 +5288,19 @@
         <v>0</v>
       </c>
       <c r="F57" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" s="7">
         <v>0</v>
@@ -5318,51 +5368,45 @@
       <c r="AF57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="7">
-        <f>water!D41</f>
         <v>0</v>
       </c>
       <c r="E58" s="7">
-        <f>glucose!D41</f>
         <v>0</v>
       </c>
       <c r="F58" s="7">
-        <f>sucrose!D41</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="7">
-        <f>'milk choc'!D41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="13">
-        <f>'milk chocolate arabinose'!D41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="7">
-        <f>'gastic milk choc'!D41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="7">
-        <f>'gastic milk choc arab'!D41</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" s="7">
-        <f>emulsie!D41</f>
         <v>0</v>
       </c>
       <c r="L58" s="7">
-        <f>arabinose!D41</f>
         <v>0</v>
       </c>
       <c r="M58" s="7">
@@ -5425,51 +5469,54 @@
       <c r="AF58" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="7">
-        <f>water!D42</f>
+        <f>water!D41</f>
         <v>0</v>
       </c>
       <c r="E59" s="7">
-        <f>glucose!D42</f>
+        <f>glucose!D41</f>
         <v>0</v>
       </c>
       <c r="F59" s="7">
-        <f>sucrose!D42</f>
+        <f>sucrose!D41</f>
         <v>0</v>
       </c>
       <c r="G59" s="7">
-        <f>'milk choc'!D42</f>
+        <f>'milk choc'!D41</f>
         <v>0</v>
       </c>
       <c r="H59" s="13">
-        <f>'milk chocolate arabinose'!D42</f>
+        <f>'milk chocolate arabinose'!D41</f>
         <v>0</v>
       </c>
       <c r="I59" s="7">
-        <f>'gastic milk choc'!D42</f>
+        <f>'gastic milk choc'!D41</f>
         <v>0</v>
       </c>
       <c r="J59" s="7">
-        <f>'gastic milk choc arab'!D42</f>
+        <f>'gastic milk choc arab'!D41</f>
         <v>0</v>
       </c>
       <c r="K59" s="7">
-        <f>emulsie!D42</f>
+        <f>emulsie!D41</f>
         <v>0</v>
       </c>
       <c r="L59" s="7">
-        <f>arabinose!D42</f>
+        <f>arabinose!D41</f>
         <v>0</v>
       </c>
       <c r="M59" s="7">
@@ -5532,51 +5579,54 @@
       <c r="AF59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D60" s="7">
-        <f>water!D43</f>
+        <f>water!D42</f>
         <v>0</v>
       </c>
       <c r="E60" s="7">
-        <f>glucose!D43</f>
+        <f>glucose!D42</f>
         <v>0</v>
       </c>
       <c r="F60" s="7">
-        <f>sucrose!D43</f>
+        <f>sucrose!D42</f>
         <v>0</v>
       </c>
       <c r="G60" s="7">
-        <f>'milk choc'!D43</f>
+        <f>'milk choc'!D42</f>
         <v>0</v>
       </c>
       <c r="H60" s="13">
-        <f>'milk chocolate arabinose'!D43</f>
+        <f>'milk chocolate arabinose'!D42</f>
         <v>0</v>
       </c>
       <c r="I60" s="7">
-        <f>'gastic milk choc'!D43</f>
+        <f>'gastic milk choc'!D42</f>
         <v>0</v>
       </c>
       <c r="J60" s="7">
-        <f>'gastic milk choc arab'!D43</f>
+        <f>'gastic milk choc arab'!D42</f>
         <v>0</v>
       </c>
       <c r="K60" s="7">
-        <f>emulsie!D43</f>
+        <f>emulsie!D42</f>
         <v>0</v>
       </c>
       <c r="L60" s="7">
-        <f>arabinose!D43</f>
+        <f>arabinose!D42</f>
         <v>0</v>
       </c>
       <c r="M60" s="7">
@@ -5639,51 +5689,54 @@
       <c r="AF60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="7">
-        <f>water!D44</f>
+        <f>water!D43</f>
         <v>0</v>
       </c>
       <c r="E61" s="7">
-        <f>glucose!D44</f>
+        <f>glucose!D43</f>
         <v>0</v>
       </c>
       <c r="F61" s="7">
-        <f>sucrose!D44</f>
+        <f>sucrose!D43</f>
         <v>0</v>
       </c>
       <c r="G61" s="7">
-        <f>'milk choc'!D44</f>
+        <f>'milk choc'!D43</f>
         <v>0</v>
       </c>
       <c r="H61" s="13">
-        <f>'milk chocolate arabinose'!D44</f>
+        <f>'milk chocolate arabinose'!D43</f>
         <v>0</v>
       </c>
       <c r="I61" s="7">
-        <f>'gastic milk choc'!D44</f>
+        <f>'gastic milk choc'!D43</f>
         <v>0</v>
       </c>
       <c r="J61" s="7">
-        <f>'gastic milk choc arab'!D44</f>
+        <f>'gastic milk choc arab'!D43</f>
         <v>0</v>
       </c>
       <c r="K61" s="7">
-        <f>emulsie!D44</f>
+        <f>emulsie!D43</f>
         <v>0</v>
       </c>
       <c r="L61" s="7">
-        <f>arabinose!D44</f>
+        <f>arabinose!D43</f>
         <v>0</v>
       </c>
       <c r="M61" s="7">
@@ -5746,51 +5799,54 @@
       <c r="AF61" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D62" s="7">
-        <f>water!D45</f>
+        <f>water!D44</f>
         <v>0</v>
       </c>
       <c r="E62" s="7">
-        <f>glucose!D45</f>
+        <f>glucose!D44</f>
         <v>0</v>
       </c>
       <c r="F62" s="7">
-        <f>sucrose!D45</f>
+        <f>sucrose!D44</f>
         <v>0</v>
       </c>
       <c r="G62" s="7">
-        <f>'milk choc'!D45</f>
+        <f>'milk choc'!D44</f>
         <v>0</v>
       </c>
       <c r="H62" s="13">
-        <f>'milk chocolate arabinose'!D45</f>
+        <f>'milk chocolate arabinose'!D44</f>
         <v>0</v>
       </c>
       <c r="I62" s="7">
-        <f>'gastic milk choc'!D45</f>
+        <f>'gastic milk choc'!D44</f>
         <v>0</v>
       </c>
       <c r="J62" s="7">
-        <f>'gastic milk choc arab'!D45</f>
+        <f>'gastic milk choc arab'!D44</f>
         <v>0</v>
       </c>
       <c r="K62" s="7">
-        <f>emulsie!D45</f>
+        <f>emulsie!D44</f>
         <v>0</v>
       </c>
       <c r="L62" s="7">
-        <f>arabinose!D45</f>
+        <f>arabinose!D44</f>
         <v>0</v>
       </c>
       <c r="M62" s="7">
@@ -5853,51 +5909,54 @@
       <c r="AF62" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D63" s="7">
-        <f>water!D46</f>
+        <f>water!D45</f>
         <v>0</v>
       </c>
       <c r="E63" s="7">
-        <f>glucose!D46</f>
+        <f>glucose!D45</f>
         <v>0</v>
       </c>
       <c r="F63" s="7">
-        <f>sucrose!D46</f>
+        <f>sucrose!D45</f>
         <v>0</v>
       </c>
       <c r="G63" s="7">
-        <f>'milk choc'!D46</f>
+        <f>'milk choc'!D45</f>
         <v>0</v>
       </c>
       <c r="H63" s="13">
-        <f>'milk chocolate arabinose'!D46</f>
+        <f>'milk chocolate arabinose'!D45</f>
         <v>0</v>
       </c>
       <c r="I63" s="7">
-        <f>'gastic milk choc'!D46</f>
+        <f>'gastic milk choc'!D45</f>
         <v>0</v>
       </c>
       <c r="J63" s="7">
-        <f>'gastic milk choc arab'!D46</f>
+        <f>'gastic milk choc arab'!D45</f>
         <v>0</v>
       </c>
       <c r="K63" s="7">
-        <f>emulsie!D46</f>
+        <f>emulsie!D45</f>
         <v>0</v>
       </c>
       <c r="L63" s="7">
-        <f>arabinose!D46</f>
+        <f>arabinose!D45</f>
         <v>0</v>
       </c>
       <c r="M63" s="7">
@@ -5960,51 +6019,54 @@
       <c r="AF63" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D64" s="7">
-        <f>water!D47</f>
+        <f>water!D46</f>
         <v>0</v>
       </c>
       <c r="E64" s="7">
-        <f>glucose!D47</f>
+        <f>glucose!D46</f>
         <v>0</v>
       </c>
       <c r="F64" s="7">
-        <f>sucrose!D47</f>
+        <f>sucrose!D46</f>
         <v>0</v>
       </c>
       <c r="G64" s="7">
-        <f>'milk choc'!D47</f>
+        <f>'milk choc'!D46</f>
         <v>0</v>
       </c>
       <c r="H64" s="13">
-        <f>'milk chocolate arabinose'!D47</f>
+        <f>'milk chocolate arabinose'!D46</f>
         <v>0</v>
       </c>
       <c r="I64" s="7">
-        <f>'gastic milk choc'!D47</f>
+        <f>'gastic milk choc'!D46</f>
         <v>0</v>
       </c>
       <c r="J64" s="7">
-        <f>'gastic milk choc arab'!D47</f>
+        <f>'gastic milk choc arab'!D46</f>
         <v>0</v>
       </c>
       <c r="K64" s="7">
-        <f>emulsie!D47</f>
+        <f>emulsie!D46</f>
         <v>0</v>
       </c>
       <c r="L64" s="7">
-        <f>arabinose!D47</f>
+        <f>arabinose!D46</f>
         <v>0</v>
       </c>
       <c r="M64" s="7">
@@ -6067,51 +6129,54 @@
       <c r="AF64" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="7">
-        <f>water!D48</f>
+        <f>water!D47</f>
         <v>0</v>
       </c>
       <c r="E65" s="7">
-        <f>glucose!D48</f>
+        <f>glucose!D47</f>
         <v>0</v>
       </c>
       <c r="F65" s="7">
-        <f>sucrose!D48</f>
+        <f>sucrose!D47</f>
         <v>0</v>
       </c>
       <c r="G65" s="7">
-        <f>'milk choc'!D48</f>
+        <f>'milk choc'!D47</f>
         <v>0</v>
       </c>
       <c r="H65" s="13">
-        <f>'milk chocolate arabinose'!D48</f>
+        <f>'milk chocolate arabinose'!D47</f>
         <v>0</v>
       </c>
       <c r="I65" s="7">
-        <f>'gastic milk choc'!D48</f>
+        <f>'gastic milk choc'!D47</f>
         <v>0</v>
       </c>
       <c r="J65" s="7">
-        <f>'gastic milk choc arab'!D48</f>
+        <f>'gastic milk choc arab'!D47</f>
         <v>0</v>
       </c>
       <c r="K65" s="7">
-        <f>emulsie!D48</f>
+        <f>emulsie!D47</f>
         <v>0</v>
       </c>
       <c r="L65" s="7">
-        <f>arabinose!D48</f>
+        <f>arabinose!D47</f>
         <v>0</v>
       </c>
       <c r="M65" s="7">
@@ -6174,51 +6239,54 @@
       <c r="AF65" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D66" s="7">
-        <f>water!D49</f>
+        <f>water!D48</f>
         <v>0</v>
       </c>
       <c r="E66" s="7">
-        <f>glucose!D49</f>
+        <f>glucose!D48</f>
         <v>0</v>
       </c>
       <c r="F66" s="7">
-        <f>sucrose!D49</f>
+        <f>sucrose!D48</f>
         <v>0</v>
       </c>
       <c r="G66" s="7">
-        <f>'milk choc'!D49</f>
+        <f>'milk choc'!D48</f>
         <v>0</v>
       </c>
       <c r="H66" s="13">
-        <f>'milk chocolate arabinose'!D49</f>
+        <f>'milk chocolate arabinose'!D48</f>
         <v>0</v>
       </c>
       <c r="I66" s="7">
-        <f>'gastic milk choc'!D49</f>
+        <f>'gastic milk choc'!D48</f>
         <v>0</v>
       </c>
       <c r="J66" s="7">
-        <f>'gastic milk choc arab'!D49</f>
+        <f>'gastic milk choc arab'!D48</f>
         <v>0</v>
       </c>
       <c r="K66" s="7">
-        <f>emulsie!D49</f>
+        <f>emulsie!D48</f>
         <v>0</v>
       </c>
       <c r="L66" s="7">
-        <f>arabinose!D49</f>
+        <f>arabinose!D48</f>
         <v>0</v>
       </c>
       <c r="M66" s="7">
@@ -6281,51 +6349,54 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D67" s="7">
-        <f>water!D50</f>
+        <f>water!D49</f>
         <v>0</v>
       </c>
       <c r="E67" s="7">
-        <f>glucose!D50</f>
+        <f>glucose!D49</f>
         <v>0</v>
       </c>
       <c r="F67" s="7">
-        <f>sucrose!D50</f>
+        <f>sucrose!D49</f>
         <v>0</v>
       </c>
       <c r="G67" s="7">
-        <f>'milk choc'!D50</f>
+        <f>'milk choc'!D49</f>
         <v>0</v>
       </c>
       <c r="H67" s="13">
-        <f>'milk chocolate arabinose'!D50</f>
+        <f>'milk chocolate arabinose'!D49</f>
         <v>0</v>
       </c>
       <c r="I67" s="7">
-        <f>'gastic milk choc'!D50</f>
+        <f>'gastic milk choc'!D49</f>
         <v>0</v>
       </c>
       <c r="J67" s="7">
-        <f>'gastic milk choc arab'!D50</f>
+        <f>'gastic milk choc arab'!D49</f>
         <v>0</v>
       </c>
       <c r="K67" s="7">
-        <f>emulsie!D50</f>
+        <f>emulsie!D49</f>
         <v>0</v>
       </c>
       <c r="L67" s="7">
-        <f>arabinose!D50</f>
+        <f>arabinose!D49</f>
         <v>0</v>
       </c>
       <c r="M67" s="7">
@@ -6388,51 +6459,54 @@
       <c r="AF67" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="7">
-        <f>water!D51</f>
+        <f>water!D50</f>
         <v>0</v>
       </c>
       <c r="E68" s="7">
-        <f>glucose!D51</f>
+        <f>glucose!D50</f>
         <v>0</v>
       </c>
       <c r="F68" s="7">
-        <f>sucrose!D51</f>
+        <f>sucrose!D50</f>
         <v>0</v>
       </c>
       <c r="G68" s="7">
-        <f>'milk choc'!D51</f>
+        <f>'milk choc'!D50</f>
         <v>0</v>
       </c>
       <c r="H68" s="13">
-        <f>'milk chocolate arabinose'!D51</f>
+        <f>'milk chocolate arabinose'!D50</f>
         <v>0</v>
       </c>
       <c r="I68" s="7">
-        <f>'gastic milk choc'!D51</f>
+        <f>'gastic milk choc'!D50</f>
         <v>0</v>
       </c>
       <c r="J68" s="7">
-        <f>'gastic milk choc arab'!D51</f>
+        <f>'gastic milk choc arab'!D50</f>
         <v>0</v>
       </c>
       <c r="K68" s="7">
-        <f>emulsie!D51</f>
+        <f>emulsie!D50</f>
         <v>0</v>
       </c>
       <c r="L68" s="7">
-        <f>arabinose!D51</f>
+        <f>arabinose!D50</f>
         <v>0</v>
       </c>
       <c r="M68" s="7">
@@ -6495,51 +6569,54 @@
       <c r="AF68" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
+        <v>58</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D69" s="7">
-        <f>water!D52</f>
+        <f>water!D51</f>
         <v>0</v>
       </c>
       <c r="E69" s="7">
-        <f>glucose!D52</f>
+        <f>glucose!D51</f>
         <v>0</v>
       </c>
       <c r="F69" s="7">
-        <f>sucrose!D52</f>
+        <f>sucrose!D51</f>
         <v>0</v>
       </c>
       <c r="G69" s="7">
-        <f>'milk choc'!D52</f>
+        <f>'milk choc'!D51</f>
         <v>0</v>
       </c>
       <c r="H69" s="13">
-        <f>'milk chocolate arabinose'!D52</f>
+        <f>'milk chocolate arabinose'!D51</f>
         <v>0</v>
       </c>
       <c r="I69" s="7">
-        <f>'gastic milk choc'!D52</f>
+        <f>'gastic milk choc'!D51</f>
         <v>0</v>
       </c>
       <c r="J69" s="7">
-        <f>'gastic milk choc arab'!D52</f>
+        <f>'gastic milk choc arab'!D51</f>
         <v>0</v>
       </c>
       <c r="K69" s="7">
-        <f>emulsie!D52</f>
+        <f>emulsie!D51</f>
         <v>0</v>
       </c>
       <c r="L69" s="7">
-        <f>arabinose!D52</f>
+        <f>arabinose!D51</f>
         <v>0</v>
       </c>
       <c r="M69" s="7">
@@ -6602,265 +6679,274 @@
       <c r="AF69" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
+        <v>60</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D70" s="7">
+        <f>water!D52</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="7">
+        <f>glucose!D52</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="7">
+        <f>sucrose!D52</f>
+        <v>0</v>
+      </c>
+      <c r="G70" s="7">
+        <f>'milk choc'!D52</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="13">
+        <f>'milk chocolate arabinose'!D52</f>
+        <v>0</v>
+      </c>
+      <c r="I70" s="7">
+        <f>'gastic milk choc'!D52</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="7">
+        <f>'gastic milk choc arab'!D52</f>
+        <v>0</v>
+      </c>
+      <c r="K70" s="7">
+        <f>emulsie!D52</f>
+        <v>0</v>
+      </c>
+      <c r="L70" s="7">
+        <f>arabinose!D52</f>
+        <v>0</v>
+      </c>
+      <c r="M70" s="7">
+        <v>0</v>
+      </c>
+      <c r="N70" s="7">
+        <v>0</v>
+      </c>
+      <c r="O70" s="7">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70" s="7">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A71" s="7">
+        <v>61</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71" s="7">
         <f>water!D53</f>
         <v>0</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E71" s="7">
         <f>glucose!D53</f>
         <v>0</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F71" s="7">
         <f>sucrose!D53</f>
         <v>0</v>
       </c>
-      <c r="G70" s="7">
+      <c r="G71" s="7">
         <f>'milk choc'!D53</f>
         <v>9</v>
       </c>
-      <c r="H70" s="13">
+      <c r="H71" s="13">
         <f>'milk chocolate arabinose'!D53</f>
         <v>9</v>
       </c>
-      <c r="I70" s="7">
+      <c r="I71" s="7">
         <f>'gastic milk choc'!D53</f>
         <v>2.31</v>
       </c>
-      <c r="J70" s="7">
+      <c r="J71" s="7">
         <f>'gastic milk choc arab'!D53</f>
         <v>2.31</v>
       </c>
-      <c r="K70" s="7">
+      <c r="K71" s="7">
         <f>emulsie!D53</f>
         <v>0</v>
       </c>
-      <c r="L70" s="7">
+      <c r="L71" s="7">
         <f>arabinose!D53</f>
         <v>0</v>
       </c>
-      <c r="M70" s="7">
-        <v>0</v>
-      </c>
-      <c r="N70" s="7">
-        <v>0</v>
-      </c>
-      <c r="O70" s="7">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70" s="7">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="1">
+      <c r="M71" s="7">
+        <v>0</v>
+      </c>
+      <c r="N71" s="7">
+        <v>0</v>
+      </c>
+      <c r="O71" s="7">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71" s="7">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="1">
         <v>100</v>
       </c>
-      <c r="AD70" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE70" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF70" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A71" s="7">
+      <c r="AD71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A72" s="7">
         <v>62</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B72" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D71" s="7">
-        <f>water!D54</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="7">
-        <f>glucose!D54</f>
-        <v>0</v>
-      </c>
-      <c r="F71" s="7">
-        <f>sucrose!D54</f>
-        <v>0</v>
-      </c>
-      <c r="G71" s="7">
-        <f>'milk choc'!D54</f>
-        <v>0</v>
-      </c>
-      <c r="H71" s="13">
-        <f>'milk chocolate arabinose'!D54</f>
-        <v>0</v>
-      </c>
-      <c r="I71" s="7">
-        <f>'gastic milk choc'!D54</f>
-        <v>0</v>
-      </c>
-      <c r="J71" s="7">
-        <f>'gastic milk choc arab'!D54</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="7">
-        <f>emulsie!D54</f>
-        <v>0</v>
-      </c>
-      <c r="L71" s="7">
-        <f>arabinose!D54</f>
-        <v>0</v>
-      </c>
-      <c r="M71" s="7">
-        <v>0</v>
-      </c>
-      <c r="N71" s="7">
-        <v>0</v>
-      </c>
-      <c r="O71" s="7">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>0</v>
-      </c>
-      <c r="R71" s="7">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>0</v>
-      </c>
-      <c r="T71">
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <v>0</v>
-      </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
-      <c r="W71">
-        <v>0</v>
-      </c>
-      <c r="X71" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z71" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB71" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC71" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD71" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE71" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A72" s="7">
-        <v>63</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D72" s="7">
-        <f>water!D55</f>
+        <f>water!D54</f>
         <v>0</v>
       </c>
       <c r="E72" s="7">
-        <f>glucose!D55</f>
+        <f>glucose!D54</f>
         <v>0</v>
       </c>
       <c r="F72" s="7">
-        <f>sucrose!D55</f>
+        <f>sucrose!D54</f>
         <v>0</v>
       </c>
       <c r="G72" s="7">
-        <f>'milk choc'!D55</f>
+        <f>'milk choc'!D54</f>
         <v>0</v>
       </c>
       <c r="H72" s="13">
-        <f>'milk chocolate arabinose'!D55</f>
+        <f>'milk chocolate arabinose'!D54</f>
         <v>0</v>
       </c>
       <c r="I72" s="7">
-        <f>'gastic milk choc'!D55</f>
+        <f>'gastic milk choc'!D54</f>
         <v>0</v>
       </c>
       <c r="J72" s="7">
-        <f>'gastic milk choc arab'!D55</f>
+        <f>'gastic milk choc arab'!D54</f>
         <v>0</v>
       </c>
       <c r="K72" s="7">
-        <f>emulsie!D55</f>
+        <f>emulsie!D54</f>
         <v>0</v>
       </c>
       <c r="L72" s="7">
-        <f>arabinose!D55</f>
+        <f>arabinose!D54</f>
         <v>0</v>
       </c>
       <c r="M72" s="7">
@@ -6923,51 +7009,54 @@
       <c r="AF72" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D73" s="7">
-        <f>water!D56</f>
+        <f>water!D55</f>
         <v>0</v>
       </c>
       <c r="E73" s="7">
-        <f>glucose!D56</f>
+        <f>glucose!D55</f>
         <v>0</v>
       </c>
       <c r="F73" s="7">
-        <f>sucrose!D56</f>
+        <f>sucrose!D55</f>
         <v>0</v>
       </c>
       <c r="G73" s="7">
-        <f>'milk choc'!D56</f>
+        <f>'milk choc'!D55</f>
         <v>0</v>
       </c>
       <c r="H73" s="13">
-        <f>'milk chocolate arabinose'!D56</f>
+        <f>'milk chocolate arabinose'!D55</f>
         <v>0</v>
       </c>
       <c r="I73" s="7">
-        <f>'gastic milk choc'!D56</f>
+        <f>'gastic milk choc'!D55</f>
         <v>0</v>
       </c>
       <c r="J73" s="7">
-        <f>'gastic milk choc arab'!D56</f>
+        <f>'gastic milk choc arab'!D55</f>
         <v>0</v>
       </c>
       <c r="K73" s="7">
-        <f>emulsie!D56</f>
+        <f>emulsie!D55</f>
         <v>0</v>
       </c>
       <c r="L73" s="7">
-        <f>arabinose!D56</f>
+        <f>arabinose!D55</f>
         <v>0</v>
       </c>
       <c r="M73" s="7">
@@ -7030,51 +7119,54 @@
       <c r="AF73" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D74" s="7">
-        <f>water!D57</f>
+        <f>water!D56</f>
         <v>0</v>
       </c>
       <c r="E74" s="7">
-        <f>glucose!D57</f>
+        <f>glucose!D56</f>
         <v>0</v>
       </c>
       <c r="F74" s="7">
-        <f>sucrose!D57</f>
+        <f>sucrose!D56</f>
         <v>0</v>
       </c>
       <c r="G74" s="7">
-        <f>'milk choc'!D57</f>
+        <f>'milk choc'!D56</f>
         <v>0</v>
       </c>
       <c r="H74" s="13">
-        <f>'milk chocolate arabinose'!D57</f>
+        <f>'milk chocolate arabinose'!D56</f>
         <v>0</v>
       </c>
       <c r="I74" s="7">
-        <f>'gastic milk choc'!D57</f>
+        <f>'gastic milk choc'!D56</f>
         <v>0</v>
       </c>
       <c r="J74" s="7">
-        <f>'gastic milk choc arab'!D57</f>
+        <f>'gastic milk choc arab'!D56</f>
         <v>0</v>
       </c>
       <c r="K74" s="7">
-        <f>emulsie!D57</f>
+        <f>emulsie!D56</f>
         <v>0</v>
       </c>
       <c r="L74" s="7">
-        <f>arabinose!D57</f>
+        <f>arabinose!D56</f>
         <v>0</v>
       </c>
       <c r="M74" s="7">
@@ -7137,51 +7229,54 @@
       <c r="AF74" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="7">
-        <f>water!D58</f>
+        <f>water!D57</f>
         <v>0</v>
       </c>
       <c r="E75" s="7">
-        <f>glucose!D58</f>
+        <f>glucose!D57</f>
         <v>0</v>
       </c>
       <c r="F75" s="7">
-        <f>sucrose!D58</f>
+        <f>sucrose!D57</f>
         <v>0</v>
       </c>
       <c r="G75" s="7">
-        <f>'milk choc'!D58</f>
+        <f>'milk choc'!D57</f>
         <v>0</v>
       </c>
       <c r="H75" s="13">
-        <f>'milk chocolate arabinose'!D58</f>
+        <f>'milk chocolate arabinose'!D57</f>
         <v>0</v>
       </c>
       <c r="I75" s="7">
-        <f>'gastic milk choc'!D58</f>
+        <f>'gastic milk choc'!D57</f>
         <v>0</v>
       </c>
       <c r="J75" s="7">
-        <f>'gastic milk choc arab'!D58</f>
+        <f>'gastic milk choc arab'!D57</f>
         <v>0</v>
       </c>
       <c r="K75" s="7">
-        <f>emulsie!D58</f>
+        <f>emulsie!D57</f>
         <v>0</v>
       </c>
       <c r="L75" s="7">
-        <f>arabinose!D58</f>
+        <f>arabinose!D57</f>
         <v>0</v>
       </c>
       <c r="M75" s="7">
@@ -7244,530 +7339,557 @@
       <c r="AF75" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D76" s="7">
+        <f>water!D58</f>
+        <v>0</v>
+      </c>
+      <c r="E76" s="7">
+        <f>glucose!D58</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="7">
+        <f>sucrose!D58</f>
+        <v>0</v>
+      </c>
+      <c r="G76" s="7">
+        <f>'milk choc'!D58</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="13">
+        <f>'milk chocolate arabinose'!D58</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="7">
+        <f>'gastic milk choc'!D58</f>
+        <v>0</v>
+      </c>
+      <c r="J76" s="7">
+        <f>'gastic milk choc arab'!D58</f>
+        <v>0</v>
+      </c>
+      <c r="K76" s="7">
+        <f>emulsie!D58</f>
+        <v>0</v>
+      </c>
+      <c r="L76" s="7">
+        <f>arabinose!D58</f>
+        <v>0</v>
+      </c>
+      <c r="M76" s="7">
+        <v>0</v>
+      </c>
+      <c r="N76" s="7">
+        <v>0</v>
+      </c>
+      <c r="O76" s="7">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76" s="7">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A77" s="7">
+        <v>67</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" s="7">
         <f>water!D59</f>
         <v>0</v>
       </c>
-      <c r="E76" s="7">
+      <c r="E77" s="7">
         <f>glucose!D59</f>
         <v>0</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F77" s="7">
         <f>sucrose!D59</f>
         <v>0</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G77" s="7">
         <f>'milk choc'!D59</f>
         <v>10</v>
       </c>
-      <c r="H76" s="13">
+      <c r="H77" s="13">
         <f>'milk chocolate arabinose'!D59</f>
         <v>10</v>
       </c>
-      <c r="I76" s="7">
+      <c r="I77" s="7">
         <f>'gastic milk choc'!D59</f>
         <v>8.59</v>
       </c>
-      <c r="J76" s="7">
+      <c r="J77" s="7">
         <f>'gastic milk choc arab'!D59</f>
         <v>8.59</v>
       </c>
-      <c r="K76" s="7">
+      <c r="K77" s="7">
         <f>emulsie!D59</f>
         <v>0</v>
       </c>
-      <c r="L76" s="7">
+      <c r="L77" s="7">
         <f>arabinose!D59</f>
         <v>0</v>
       </c>
-      <c r="M76" s="7">
-        <v>0</v>
-      </c>
-      <c r="N76" s="7">
-        <v>0</v>
-      </c>
-      <c r="O76" s="7">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>0</v>
-      </c>
-      <c r="R76" s="7">
-        <v>0</v>
-      </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
-      </c>
-      <c r="V76">
-        <v>0</v>
-      </c>
-      <c r="W76">
-        <v>0</v>
-      </c>
-      <c r="X76" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="8">
+      <c r="M77" s="7">
+        <v>0</v>
+      </c>
+      <c r="N77" s="7">
+        <v>0</v>
+      </c>
+      <c r="O77" s="7">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77" s="7">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="8">
         <v>100</v>
       </c>
-      <c r="AC76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF76" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A77" s="7">
+      <c r="AC77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>68</v>
+      </c>
+      <c r="B78" t="s">
+        <v>118</v>
+      </c>
+      <c r="C78" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="7">
+        <v>0</v>
+      </c>
+      <c r="E78" s="7">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0</v>
+      </c>
+      <c r="O78" s="1">
+        <v>0</v>
+      </c>
+      <c r="P78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>0</v>
+      </c>
+      <c r="R78" s="1">
+        <v>0</v>
+      </c>
+      <c r="S78" s="1">
+        <v>0</v>
+      </c>
+      <c r="T78" s="1">
+        <v>0</v>
+      </c>
+      <c r="U78" s="1">
+        <v>0</v>
+      </c>
+      <c r="V78" s="1">
+        <v>0</v>
+      </c>
+      <c r="W78" s="1">
+        <v>0</v>
+      </c>
+      <c r="X78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A79" s="7">
         <v>70</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B79" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C79" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D79" s="7">
         <f>water!D60</f>
         <v>0</v>
       </c>
-      <c r="E77" s="7">
+      <c r="E79" s="7">
         <f>glucose!D60</f>
         <v>0</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F79" s="7">
         <f>sucrose!D60</f>
         <v>0</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G79" s="7">
         <f>'milk choc'!D60</f>
         <v>0</v>
       </c>
-      <c r="H77" s="13">
+      <c r="H79" s="13">
         <f>'milk chocolate arabinose'!D60</f>
         <v>0</v>
       </c>
-      <c r="I77" s="7">
+      <c r="I79" s="7">
         <f>'gastic milk choc'!D60</f>
         <v>0</v>
       </c>
-      <c r="J77" s="7">
+      <c r="J79" s="7">
         <f>'gastic milk choc arab'!D60</f>
         <v>0</v>
       </c>
-      <c r="K77" s="7">
+      <c r="K79" s="7">
         <f>emulsie!D60</f>
         <v>0</v>
       </c>
-      <c r="L77" s="7">
+      <c r="L79" s="7">
         <f>arabinose!D60</f>
         <v>0</v>
       </c>
-      <c r="M77" s="7">
-        <v>0</v>
-      </c>
-      <c r="N77" s="7">
-        <v>0</v>
-      </c>
-      <c r="O77" s="7">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>0</v>
-      </c>
-      <c r="R77" s="7">
-        <v>0</v>
-      </c>
-      <c r="S77">
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>0</v>
-      </c>
-      <c r="V77">
-        <v>0</v>
-      </c>
-      <c r="W77">
-        <v>0</v>
-      </c>
-      <c r="X77" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF77" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A78" s="7">
+      <c r="M79" s="7">
+        <v>0</v>
+      </c>
+      <c r="N79" s="7">
+        <v>0</v>
+      </c>
+      <c r="O79" s="7">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79" s="7">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A80" s="7">
         <v>71</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B80" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D80" s="7">
         <f>water!D61</f>
         <v>0</v>
       </c>
-      <c r="E78" s="7">
+      <c r="E80" s="7">
         <f>glucose!D61</f>
         <v>0</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F80" s="7">
         <f>sucrose!D61</f>
         <v>0</v>
       </c>
-      <c r="G78" s="7">
+      <c r="G80" s="7">
         <f>'milk choc'!D61</f>
         <v>0</v>
       </c>
-      <c r="H78" s="13">
+      <c r="H80" s="13">
         <f>'milk chocolate arabinose'!D61</f>
         <v>0</v>
       </c>
-      <c r="I78" s="7">
+      <c r="I80" s="7">
         <f>'gastic milk choc'!D61</f>
         <v>0</v>
       </c>
-      <c r="J78" s="7">
+      <c r="J80" s="7">
         <f>'gastic milk choc arab'!D61</f>
         <v>0</v>
       </c>
-      <c r="K78" s="7">
+      <c r="K80" s="7">
         <f>emulsie!D61</f>
         <v>0</v>
       </c>
-      <c r="L78" s="7">
+      <c r="L80" s="7">
         <f>arabinose!D61</f>
         <v>0</v>
       </c>
-      <c r="M78" s="7">
-        <v>0</v>
-      </c>
-      <c r="N78" s="7">
-        <v>0</v>
-      </c>
-      <c r="O78" s="7">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>0</v>
-      </c>
-      <c r="R78" s="7">
-        <v>0</v>
-      </c>
-      <c r="S78">
-        <v>0</v>
-      </c>
-      <c r="T78">
-        <v>0</v>
-      </c>
-      <c r="U78">
-        <v>0</v>
-      </c>
-      <c r="V78">
-        <v>0</v>
-      </c>
-      <c r="W78">
-        <v>0</v>
-      </c>
-      <c r="X78" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF78" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A79">
+      <c r="M80" s="7">
+        <v>0</v>
+      </c>
+      <c r="N80" s="7">
+        <v>0</v>
+      </c>
+      <c r="O80" s="7">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80" s="7">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A81">
         <v>72</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B81" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="C79" t="s">
-        <v>28</v>
-      </c>
-      <c r="D79" s="7">
-        <v>0</v>
-      </c>
-      <c r="E79" s="7">
-        <v>0</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="G79">
-        <v>0</v>
-      </c>
-      <c r="H79" s="21">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
-        <v>0</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="1">
-        <v>0</v>
-      </c>
-      <c r="R79" s="1">
-        <v>0</v>
-      </c>
-      <c r="S79" s="1">
-        <v>0</v>
-      </c>
-      <c r="T79" s="1">
-        <v>0</v>
-      </c>
-      <c r="U79" s="1">
-        <v>0</v>
-      </c>
-      <c r="V79" s="1">
-        <v>0</v>
-      </c>
-      <c r="W79" s="7">
-        <v>0</v>
-      </c>
-      <c r="X79" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y79" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z79" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="20">
-        <v>0</v>
-      </c>
-      <c r="AB79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD79" s="1">
-        <v>100</v>
-      </c>
-      <c r="AE79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF79" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>73</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C80" t="s">
-        <v>28</v>
-      </c>
-      <c r="D80" s="7">
-        <v>0</v>
-      </c>
-      <c r="E80" s="7">
-        <v>0</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-      <c r="G80">
-        <v>0</v>
-      </c>
-      <c r="H80" s="21">
-        <v>0</v>
-      </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="1">
-        <v>0</v>
-      </c>
-      <c r="R80" s="1">
-        <v>0</v>
-      </c>
-      <c r="S80" s="1">
-        <v>0</v>
-      </c>
-      <c r="T80" s="1">
-        <v>0</v>
-      </c>
-      <c r="U80" s="1">
-        <v>0</v>
-      </c>
-      <c r="V80" s="1">
-        <v>0</v>
-      </c>
-      <c r="W80" s="20">
-        <v>0</v>
-      </c>
-      <c r="X80" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="20">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="1">
-        <v>100</v>
-      </c>
-      <c r="AF80" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>74</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>117</v>
       </c>
       <c r="C81" t="s">
         <v>28</v>
@@ -7829,7 +7951,7 @@
       <c r="V81" s="1">
         <v>0</v>
       </c>
-      <c r="W81" s="20">
+      <c r="W81" s="7">
         <v>0</v>
       </c>
       <c r="X81" s="20">
@@ -7851,576 +7973,797 @@
         <v>0</v>
       </c>
       <c r="AD81" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE81" s="1">
         <v>0</v>
       </c>
       <c r="AF81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>73</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="7">
+        <v>0</v>
+      </c>
+      <c r="E82" s="7">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82" s="21">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>0</v>
+      </c>
+      <c r="R82" s="1">
+        <v>0</v>
+      </c>
+      <c r="S82" s="1">
+        <v>0</v>
+      </c>
+      <c r="T82" s="1">
+        <v>0</v>
+      </c>
+      <c r="U82" s="1">
+        <v>0</v>
+      </c>
+      <c r="V82" s="1">
+        <v>0</v>
+      </c>
+      <c r="W82" s="20">
+        <v>0</v>
+      </c>
+      <c r="X82" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A82" s="7">
+      <c r="AF82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>74</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" s="7">
+        <v>0</v>
+      </c>
+      <c r="E83" s="7">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83" s="21">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>0</v>
+      </c>
+      <c r="R83" s="1">
+        <v>0</v>
+      </c>
+      <c r="S83" s="1">
+        <v>0</v>
+      </c>
+      <c r="T83" s="1">
+        <v>0</v>
+      </c>
+      <c r="U83" s="1">
+        <v>0</v>
+      </c>
+      <c r="V83" s="1">
+        <v>0</v>
+      </c>
+      <c r="W83" s="20">
+        <v>0</v>
+      </c>
+      <c r="X83" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="1">
+        <v>100</v>
+      </c>
+      <c r="AG83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A84" s="7">
         <v>78</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B84" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C84" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D84" s="7">
         <f>water!D62</f>
         <v>0</v>
       </c>
-      <c r="E82" s="7">
+      <c r="E84" s="7">
         <f>glucose!D62</f>
         <v>0</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F84" s="7">
         <f>sucrose!D62</f>
         <v>0</v>
       </c>
-      <c r="G82" s="7">
+      <c r="G84" s="7">
         <f>'milk choc'!D62</f>
         <v>0</v>
       </c>
-      <c r="H82" s="13">
+      <c r="H84" s="13">
         <f>'milk chocolate arabinose'!D62</f>
         <v>0</v>
       </c>
-      <c r="I82" s="7">
+      <c r="I84" s="7">
         <f>'gastic milk choc'!D62</f>
         <v>0</v>
       </c>
-      <c r="J82" s="7">
+      <c r="J84" s="7">
         <f>'gastic milk choc arab'!D62</f>
         <v>0</v>
       </c>
-      <c r="K82" s="7">
+      <c r="K84" s="7">
         <f>emulsie!D62</f>
         <v>0</v>
       </c>
-      <c r="L82" s="7">
+      <c r="L84" s="7">
         <f>arabinose!D62</f>
         <v>0</v>
       </c>
-      <c r="M82" s="7">
-        <v>0</v>
-      </c>
-      <c r="N82" s="7">
-        <v>0</v>
-      </c>
-      <c r="O82" s="7">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82" s="7">
-        <v>0</v>
-      </c>
-      <c r="S82">
-        <v>0</v>
-      </c>
-      <c r="T82">
-        <v>0</v>
-      </c>
-      <c r="U82">
-        <v>0</v>
-      </c>
-      <c r="V82">
-        <v>0</v>
-      </c>
-      <c r="W82">
-        <v>0</v>
-      </c>
-      <c r="X82" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z82" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB82" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF82" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A83" s="7">
+      <c r="M84" s="7">
+        <v>0</v>
+      </c>
+      <c r="N84" s="7">
+        <v>0</v>
+      </c>
+      <c r="O84" s="7">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84" s="7">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A85" s="7">
         <v>79</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B85" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C85" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D83" s="7">
+      <c r="D85" s="7">
         <f>water!D63</f>
         <v>0</v>
       </c>
-      <c r="E83" s="7">
+      <c r="E85" s="7">
         <f>glucose!D63</f>
         <v>0</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F85" s="7">
         <f>sucrose!D63</f>
         <v>0</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G85" s="7">
         <f>'milk choc'!D63</f>
         <v>0</v>
       </c>
-      <c r="H83" s="13">
+      <c r="H85" s="13">
         <f>'milk chocolate arabinose'!D63</f>
         <v>0</v>
       </c>
-      <c r="I83" s="7">
+      <c r="I85" s="7">
         <f>'gastic milk choc'!D63</f>
         <v>0</v>
       </c>
-      <c r="J83" s="7">
+      <c r="J85" s="7">
         <f>'gastic milk choc arab'!D63</f>
         <v>0</v>
       </c>
-      <c r="K83" s="7">
+      <c r="K85" s="7">
         <f>emulsie!D63</f>
         <v>0</v>
       </c>
-      <c r="L83" s="7">
+      <c r="L85" s="7">
         <f>arabinose!D63</f>
         <v>0</v>
       </c>
-      <c r="M83" s="7">
-        <v>0</v>
-      </c>
-      <c r="N83" s="7">
-        <v>0</v>
-      </c>
-      <c r="O83" s="7">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>0</v>
-      </c>
-      <c r="R83" s="7">
-        <v>0</v>
-      </c>
-      <c r="S83">
-        <v>0</v>
-      </c>
-      <c r="T83">
-        <v>0</v>
-      </c>
-      <c r="U83">
-        <v>0</v>
-      </c>
-      <c r="V83">
-        <v>0</v>
-      </c>
-      <c r="W83">
-        <v>0</v>
-      </c>
-      <c r="X83" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A84" s="7">
+      <c r="M85" s="7">
+        <v>0</v>
+      </c>
+      <c r="N85" s="7">
+        <v>0</v>
+      </c>
+      <c r="O85" s="7">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85" s="7">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+      <c r="X85" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A86" s="7">
         <v>80</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B86" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C86" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D84" s="7">
+      <c r="D86" s="7">
         <f>water!D64</f>
         <v>0</v>
       </c>
-      <c r="E84" s="7">
+      <c r="E86" s="7">
         <f>glucose!D64</f>
         <v>0</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F86" s="7">
         <f>sucrose!D64</f>
         <v>0</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G86" s="7">
         <f>'milk choc'!D64</f>
         <v>0</v>
       </c>
-      <c r="H84" s="13">
+      <c r="H86" s="13">
         <f>'milk chocolate arabinose'!D64</f>
         <v>0</v>
       </c>
-      <c r="I84" s="7">
+      <c r="I86" s="7">
         <f>'gastic milk choc'!D64</f>
         <v>0</v>
       </c>
-      <c r="J84" s="7">
+      <c r="J86" s="7">
         <f>'gastic milk choc arab'!D64</f>
         <v>0</v>
       </c>
-      <c r="K84" s="7">
+      <c r="K86" s="7">
         <f>emulsie!D64</f>
         <v>0</v>
       </c>
-      <c r="L84" s="7">
+      <c r="L86" s="7">
         <f>arabinose!D64</f>
         <v>0</v>
       </c>
-      <c r="M84" s="7">
-        <v>0</v>
-      </c>
-      <c r="N84" s="7">
-        <v>0</v>
-      </c>
-      <c r="O84" s="7">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>0</v>
-      </c>
-      <c r="R84" s="7">
-        <v>0</v>
-      </c>
-      <c r="S84">
-        <v>0</v>
-      </c>
-      <c r="T84">
-        <v>0</v>
-      </c>
-      <c r="U84">
-        <v>0</v>
-      </c>
-      <c r="V84">
-        <v>0</v>
-      </c>
-      <c r="W84">
-        <v>0</v>
-      </c>
-      <c r="X84" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z84" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA84" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB84" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC84" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD84" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE84" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF84" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A85" s="7">
-        <v>0</v>
-      </c>
-      <c r="D85" s="7">
-        <f t="shared" ref="D85:L85" si="0">SUM(D38:D84)</f>
+      <c r="M86" s="7">
+        <v>0</v>
+      </c>
+      <c r="N86" s="7">
+        <v>0</v>
+      </c>
+      <c r="O86" s="7">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86" s="7">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A87" s="7">
+        <v>0</v>
+      </c>
+      <c r="D87" s="7">
+        <f t="shared" ref="D87:L87" si="0">SUM(D39:D86)</f>
         <v>100</v>
       </c>
-      <c r="E85" s="7">
+      <c r="E87" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F87" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="G85" s="7">
+      <c r="G87" s="7">
         <f t="shared" si="0"/>
         <v>100.31</v>
       </c>
-      <c r="H85" s="7">
+      <c r="H87" s="7">
         <f t="shared" si="0"/>
         <v>100.41</v>
       </c>
-      <c r="I85" s="7">
+      <c r="I87" s="7">
         <f t="shared" si="0"/>
         <v>99.83</v>
       </c>
-      <c r="J85" s="7">
+      <c r="J87" s="7">
         <f t="shared" si="0"/>
         <v>99.83</v>
       </c>
-      <c r="K85" s="7">
+      <c r="K87" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="L85" s="7">
+      <c r="L87" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="M85" s="7">
-        <f>SUM(M38:M84)</f>
+      <c r="M87" s="7">
+        <f>SUM(M39:M86)</f>
         <v>99</v>
       </c>
-      <c r="N85" s="7">
-        <f t="shared" ref="N85:AB85" si="1">SUM(N38:N84)</f>
+      <c r="N87" s="7">
+        <f t="shared" ref="N87:AB87" si="1">SUM(N39:N86)</f>
         <v>99</v>
       </c>
-      <c r="O85" s="7">
+      <c r="O87" s="7">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-      <c r="P85">
+      <c r="P87">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="Q85">
+      <c r="Q87">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="R85" s="7">
+      <c r="R87" s="7">
         <f t="shared" si="1"/>
         <v>132</v>
       </c>
-      <c r="S85">
-        <f t="shared" ref="S85" si="2">SUM(S38:S84)</f>
+      <c r="S87">
+        <f t="shared" ref="S87" si="2">SUM(S39:S86)</f>
         <v>132</v>
       </c>
-      <c r="T85">
+      <c r="T87">
         <v>132</v>
       </c>
-      <c r="U85">
-        <f t="shared" ref="U85:AA85" si="3">SUM(U38:U84)</f>
+      <c r="U87">
+        <f t="shared" ref="U87:AA87" si="3">SUM(U39:U86)</f>
         <v>119</v>
       </c>
-      <c r="V85">
-        <f t="shared" ref="V85" si="4">SUM(V38:V84)</f>
+      <c r="V87">
+        <f t="shared" ref="V87" si="4">SUM(V39:V86)</f>
         <v>119</v>
       </c>
-      <c r="W85">
+      <c r="W87">
         <v>119</v>
       </c>
-      <c r="X85" s="7">
+      <c r="X87" s="7">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="Y85" s="7">
+      <c r="Y87" s="7">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="Z85" s="7">
+      <c r="Z87" s="7">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AA85" s="7">
+      <c r="AA87" s="7">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AB85" s="7">
+      <c r="AB87" s="7">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC85" s="7">
-        <f ca="1">SUM(AC38:AC87)</f>
+      <c r="AC87" s="7">
+        <f>SUM(AC39:AC86)</f>
         <v>100</v>
       </c>
-      <c r="AD85" s="7">
-        <f>SUM(AD38:AD84)</f>
+      <c r="AD87" s="7">
+        <f>SUM(AD39:AD86)</f>
         <v>100</v>
       </c>
-      <c r="AE85" s="7">
-        <f>SUM(AE38:AE84)</f>
+      <c r="AE87" s="7">
+        <f>SUM(AE39:AE86)</f>
         <v>100</v>
       </c>
-      <c r="AF85" s="7">
-        <f>SUM(AF38:AF84)</f>
+      <c r="AF87" s="7">
+        <f>SUM(AF39:AF86)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B86" s="7" t="s">
+      <c r="AG87" s="7">
+        <f t="shared" ref="AG87" si="5">SUM(AG39:AG86)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B88" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C88" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D88" s="7">
         <f>water!D66</f>
         <v>1</v>
       </c>
-      <c r="E86" s="7">
+      <c r="E88" s="7">
         <f>glucose!D66</f>
         <v>1.44</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F88" s="7">
         <f>sucrose!D66</f>
         <v>1.44</v>
       </c>
-      <c r="G86" s="7">
+      <c r="G88" s="7">
         <f>'milk choc'!D66</f>
         <v>1.3</v>
       </c>
-      <c r="H86" s="13">
+      <c r="H88" s="13">
         <f>'milk chocolate arabinose'!D66</f>
         <v>1.3</v>
       </c>
-      <c r="I86" s="7">
+      <c r="I88" s="7">
         <f>'gastic milk choc'!D66</f>
         <v>1.2</v>
       </c>
-      <c r="J86" s="7">
+      <c r="J88" s="7">
         <f>'gastic milk choc arab'!D66</f>
         <v>1.2</v>
       </c>
-      <c r="K86" s="7">
+      <c r="K88" s="7">
         <f>emulsie!D66</f>
         <v>0.95</v>
       </c>
-      <c r="L86" s="7">
+      <c r="L88" s="7">
         <f>arabinose!D66</f>
         <v>1.44</v>
       </c>
-      <c r="M86" s="7">
+      <c r="M88" s="7">
         <v>1.44</v>
       </c>
-      <c r="N86" s="7">
+      <c r="N88" s="7">
         <v>1.44</v>
       </c>
-      <c r="O86" s="7">
+      <c r="O88" s="7">
         <v>1.44</v>
       </c>
-      <c r="P86">
+      <c r="P88">
         <v>1.4</v>
       </c>
-      <c r="Q86">
+      <c r="Q88">
         <v>1.4</v>
       </c>
-      <c r="R86" s="7">
+      <c r="R88" s="7">
         <v>1.4</v>
       </c>
-      <c r="S86">
+      <c r="S88">
         <v>1.4</v>
       </c>
-      <c r="T86">
+      <c r="T88">
         <v>1.4</v>
       </c>
-      <c r="U86">
+      <c r="U88">
         <v>1.4</v>
       </c>
-      <c r="V86">
+      <c r="V88">
         <v>1.4</v>
       </c>
-      <c r="W86">
+      <c r="W88">
         <v>1.4</v>
       </c>
-      <c r="X86" s="7">
+      <c r="X88" s="7">
         <v>1</v>
       </c>
-      <c r="Y86" s="7">
+      <c r="Y88" s="7">
         <v>1</v>
       </c>
-      <c r="Z86" s="7">
+      <c r="Z88" s="7">
         <v>1</v>
       </c>
-      <c r="AA86" s="7">
+      <c r="AA88" s="7">
         <v>1</v>
       </c>
-      <c r="AB86" s="8">
+      <c r="AB88" s="8">
         <v>1.4</v>
       </c>
-      <c r="AC86" s="1">
+      <c r="AC88" s="1">
         <v>1.4</v>
       </c>
-      <c r="AD86" s="1">
+      <c r="AD88" s="1">
         <v>1.4</v>
       </c>
-      <c r="AE86" s="1">
+      <c r="AE88" s="1">
         <v>1.4</v>
       </c>
-      <c r="AF86" s="1">
+      <c r="AF88" s="1">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="AC87" s="1"/>
-      <c r="AD87" s="1"/>
-      <c r="AE87" s="1"/>
-      <c r="AF87" s="1"/>
+      <c r="AG88" s="22">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="89" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AC89" s="1"/>
+      <c r="AD89" s="1"/>
+      <c r="AE89" s="1"/>
+      <c r="AF89" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D16" location="water!A1" display="water" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E16" location="glucose!A1" display="glucose" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F16" location="sucrose!A1" display="sucrose" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G16" location="'milk choc'!A1" display="milk choc" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H16" location="'milk chocolate arabinose'!A1" display="milk choc arab" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="I16" location="'gastic milk choc'!A1" display="'gastic milk choc'!A1" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="J16" location="'gastic milk choc arab'!A1" display="'gastic milk choc arab'!A1" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="K16" location="emulsie!A1" display="emulsie" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="L16" location="arabinose!A1" display="arabinose" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D17" location="water!A1" display="water" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E17" location="glucose!A1" display="glucose" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F17" location="sucrose!A1" display="sucrose" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G17" location="'milk choc'!A1" display="milk choc" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H17" location="'milk chocolate arabinose'!A1" display="milk choc arab" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I17" location="'gastic milk choc'!A1" display="'gastic milk choc'!A1" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="J17" location="'gastic milk choc arab'!A1" display="'gastic milk choc arab'!A1" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K17" location="emulsie!A1" display="emulsie" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="L17" location="arabinose!A1" display="arabinose" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
